--- a/PTM/2026_PTM_SecondYr_data.xlsx
+++ b/PTM/2026_PTM_SecondYr_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026_Even\WTMA\WTMA_LAB\WTMA-Lab\PTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3197EAE8-A3AF-4780-B67E-9BB77FA1BB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E131FB-6705-4331-8DC8-1FC26F04D5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="417">
   <si>
     <t>Registration Id</t>
   </si>
@@ -1270,6 +1270,12 @@
   </si>
   <si>
     <t>Environmental Science and Engineering-M</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>No Of Arrearss</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N403"/>
+  <dimension ref="A1:O403"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1645,10 +1651,11 @@
     <col min="11" max="12" width="38.6640625" style="2" customWidth="1"/>
     <col min="13" max="13" width="38.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="44" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1691,8 +1698,11 @@
       <c r="N1" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>251801001</v>
       </c>
@@ -1735,8 +1745,11 @@
       <c r="N2" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>251801002</v>
       </c>
@@ -1779,8 +1792,11 @@
       <c r="N3" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>251801003</v>
       </c>
@@ -1823,8 +1839,11 @@
       <c r="N4" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>251801004</v>
       </c>
@@ -1867,8 +1886,11 @@
       <c r="N5" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>251801005</v>
       </c>
@@ -1911,8 +1933,11 @@
       <c r="N6" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>251801006</v>
       </c>
@@ -1955,8 +1980,11 @@
       <c r="N7" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>251801007</v>
       </c>
@@ -1999,8 +2027,11 @@
       <c r="N8" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>251801008</v>
       </c>
@@ -2043,8 +2074,11 @@
       <c r="N9" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>251801009</v>
       </c>
@@ -2087,8 +2121,11 @@
       <c r="N10" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>251801010</v>
       </c>
@@ -2131,8 +2168,11 @@
       <c r="N11" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>251801011</v>
       </c>
@@ -2175,8 +2215,11 @@
       <c r="N12" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>251801012</v>
       </c>
@@ -2219,8 +2262,11 @@
       <c r="N13" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>251801013</v>
       </c>
@@ -2263,8 +2309,11 @@
       <c r="N14" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>251801014</v>
       </c>
@@ -2307,8 +2356,11 @@
       <c r="N15" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>251801015</v>
       </c>
@@ -2351,8 +2403,11 @@
       <c r="N16" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>251801016</v>
       </c>
@@ -2395,8 +2450,11 @@
       <c r="N17" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>251801017</v>
       </c>
@@ -2439,8 +2497,11 @@
       <c r="N18" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>251801018</v>
       </c>
@@ -2483,8 +2544,11 @@
       <c r="N19" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>251801019</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="N20" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>251801020</v>
       </c>
@@ -2571,8 +2638,11 @@
       <c r="N21" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>251801021</v>
       </c>
@@ -2615,8 +2685,11 @@
       <c r="N22" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>251801022</v>
       </c>
@@ -2659,8 +2732,11 @@
       <c r="N23" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>251801023</v>
       </c>
@@ -2703,8 +2779,11 @@
       <c r="N24" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>251801024</v>
       </c>
@@ -2747,8 +2826,11 @@
       <c r="N25" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>251801025</v>
       </c>
@@ -2791,8 +2873,11 @@
       <c r="N26" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>251801026</v>
       </c>
@@ -2835,8 +2920,11 @@
       <c r="N27" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>251801027</v>
       </c>
@@ -2879,8 +2967,11 @@
       <c r="N28" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>251801028</v>
       </c>
@@ -2923,8 +3014,11 @@
       <c r="N29" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>251801029</v>
       </c>
@@ -2967,8 +3061,11 @@
       <c r="N30" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>251801030</v>
       </c>
@@ -3011,8 +3108,11 @@
       <c r="N31" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>251801031</v>
       </c>
@@ -3055,8 +3155,11 @@
       <c r="N32" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>251801032</v>
       </c>
@@ -3099,8 +3202,11 @@
       <c r="N33" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>251801033</v>
       </c>
@@ -3143,8 +3249,11 @@
       <c r="N34" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>251801034</v>
       </c>
@@ -3187,8 +3296,11 @@
       <c r="N35" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>251801035</v>
       </c>
@@ -3231,8 +3343,11 @@
       <c r="N36" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>251801036</v>
       </c>
@@ -3275,8 +3390,11 @@
       <c r="N37" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>251801037</v>
       </c>
@@ -3319,8 +3437,11 @@
       <c r="N38" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>251801038</v>
       </c>
@@ -3363,8 +3484,11 @@
       <c r="N39" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>251801039</v>
       </c>
@@ -3407,8 +3531,11 @@
       <c r="N40" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>251801040</v>
       </c>
@@ -3451,8 +3578,11 @@
       <c r="N41" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>251801041</v>
       </c>
@@ -3495,8 +3625,11 @@
       <c r="N42" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>251801042</v>
       </c>
@@ -3539,8 +3672,11 @@
       <c r="N43" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>251801043</v>
       </c>
@@ -3583,8 +3719,11 @@
       <c r="N44" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>251801044</v>
       </c>
@@ -3627,8 +3766,11 @@
       <c r="N45" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>251801045</v>
       </c>
@@ -3671,8 +3813,11 @@
       <c r="N46" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>251801046</v>
       </c>
@@ -3715,8 +3860,11 @@
       <c r="N47" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>251801047</v>
       </c>
@@ -3759,8 +3907,11 @@
       <c r="N48" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>251801048</v>
       </c>
@@ -3803,8 +3954,11 @@
       <c r="N49" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>251801049</v>
       </c>
@@ -3847,8 +4001,11 @@
       <c r="N50" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>251801050</v>
       </c>
@@ -3891,8 +4048,11 @@
       <c r="N51" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>251801051</v>
       </c>
@@ -3935,8 +4095,11 @@
       <c r="N52" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>251801052</v>
       </c>
@@ -3979,8 +4142,11 @@
       <c r="N53" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>251801053</v>
       </c>
@@ -4023,8 +4189,11 @@
       <c r="N54" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>251801054</v>
       </c>
@@ -4067,8 +4236,11 @@
       <c r="N55" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>251801055</v>
       </c>
@@ -4111,8 +4283,11 @@
       <c r="N56" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O56" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>251801056</v>
       </c>
@@ -4155,8 +4330,11 @@
       <c r="N57" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O57" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>251801057</v>
       </c>
@@ -4199,8 +4377,11 @@
       <c r="N58" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>251801058</v>
       </c>
@@ -4243,8 +4424,11 @@
       <c r="N59" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>251801059</v>
       </c>
@@ -4287,8 +4471,11 @@
       <c r="N60" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O60" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>251801060</v>
       </c>
@@ -4331,8 +4518,11 @@
       <c r="N61" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O61" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>251801061</v>
       </c>
@@ -4375,8 +4565,11 @@
       <c r="N62" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>251801062</v>
       </c>
@@ -4419,8 +4612,11 @@
       <c r="N63" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O63" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>251801063</v>
       </c>
@@ -4463,8 +4659,11 @@
       <c r="N64" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O64" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>251801064</v>
       </c>
@@ -4507,8 +4706,11 @@
       <c r="N65" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O65" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>251801065</v>
       </c>
@@ -4551,8 +4753,11 @@
       <c r="N66" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O66" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>251801066</v>
       </c>
@@ -4595,8 +4800,11 @@
       <c r="N67" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O67" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>251801067</v>
       </c>
@@ -4639,8 +4847,11 @@
       <c r="N68" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>251801068</v>
       </c>
@@ -4683,8 +4894,11 @@
       <c r="N69" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>251801069</v>
       </c>
@@ -4727,8 +4941,11 @@
       <c r="N70" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>251801070</v>
       </c>
@@ -4771,8 +4988,11 @@
       <c r="N71" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>251801071</v>
       </c>
@@ -4815,8 +5035,11 @@
       <c r="N72" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>251801072</v>
       </c>
@@ -4859,8 +5082,11 @@
       <c r="N73" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>251801073</v>
       </c>
@@ -4903,8 +5129,11 @@
       <c r="N74" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>251801074</v>
       </c>
@@ -4947,8 +5176,11 @@
       <c r="N75" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>251801075</v>
       </c>
@@ -4991,8 +5223,11 @@
       <c r="N76" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>251801076</v>
       </c>
@@ -5035,8 +5270,11 @@
       <c r="N77" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>251801078</v>
       </c>
@@ -5079,8 +5317,11 @@
       <c r="N78" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>251801079</v>
       </c>
@@ -5123,8 +5364,11 @@
       <c r="N79" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>251801080</v>
       </c>
@@ -5167,8 +5411,11 @@
       <c r="N80" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>251801081</v>
       </c>
@@ -5211,8 +5458,11 @@
       <c r="N81" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>251801082</v>
       </c>
@@ -5255,8 +5505,11 @@
       <c r="N82" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>251801083</v>
       </c>
@@ -5299,8 +5552,11 @@
       <c r="N83" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>251801084</v>
       </c>
@@ -5343,8 +5599,11 @@
       <c r="N84" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>251801085</v>
       </c>
@@ -5387,8 +5646,11 @@
       <c r="N85" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>251801086</v>
       </c>
@@ -5431,8 +5693,11 @@
       <c r="N86" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>251801087</v>
       </c>
@@ -5475,8 +5740,11 @@
       <c r="N87" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>251801088</v>
       </c>
@@ -5519,8 +5787,11 @@
       <c r="N88" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>251801089</v>
       </c>
@@ -5563,8 +5834,11 @@
       <c r="N89" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>251801090</v>
       </c>
@@ -5607,8 +5881,11 @@
       <c r="N90" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>251801091</v>
       </c>
@@ -5651,8 +5928,11 @@
       <c r="N91" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>251801092</v>
       </c>
@@ -5695,8 +5975,11 @@
       <c r="N92" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>251801093</v>
       </c>
@@ -5739,8 +6022,11 @@
       <c r="N93" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>251801094</v>
       </c>
@@ -5783,8 +6069,11 @@
       <c r="N94" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>251801095</v>
       </c>
@@ -5827,8 +6116,11 @@
       <c r="N95" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>251801096</v>
       </c>
@@ -5871,8 +6163,11 @@
       <c r="N96" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>251801097</v>
       </c>
@@ -5915,8 +6210,11 @@
       <c r="N97" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>251801098</v>
       </c>
@@ -5959,8 +6257,11 @@
       <c r="N98" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>251801099</v>
       </c>
@@ -6003,8 +6304,11 @@
       <c r="N99" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>251801100</v>
       </c>
@@ -6047,8 +6351,11 @@
       <c r="N100" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>251801101</v>
       </c>
@@ -6091,8 +6398,11 @@
       <c r="N101" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>251801102</v>
       </c>
@@ -6135,8 +6445,11 @@
       <c r="N102" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>251801103</v>
       </c>
@@ -6179,8 +6492,11 @@
       <c r="N103" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>251801104</v>
       </c>
@@ -6223,8 +6539,11 @@
       <c r="N104" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>251801105</v>
       </c>
@@ -6267,8 +6586,11 @@
       <c r="N105" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>251801106</v>
       </c>
@@ -6311,8 +6633,11 @@
       <c r="N106" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>251801107</v>
       </c>
@@ -6355,8 +6680,11 @@
       <c r="N107" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>251801108</v>
       </c>
@@ -6399,8 +6727,11 @@
       <c r="N108" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>251801109</v>
       </c>
@@ -6443,8 +6774,11 @@
       <c r="N109" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>251801110</v>
       </c>
@@ -6487,8 +6821,11 @@
       <c r="N110" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>251801111</v>
       </c>
@@ -6531,8 +6868,11 @@
       <c r="N111" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>251801112</v>
       </c>
@@ -6575,8 +6915,11 @@
       <c r="N112" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>251801113</v>
       </c>
@@ -6619,8 +6962,11 @@
       <c r="N113" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>251801114</v>
       </c>
@@ -6663,8 +7009,11 @@
       <c r="N114" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>251801115</v>
       </c>
@@ -6707,8 +7056,11 @@
       <c r="N115" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O115" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>251801116</v>
       </c>
@@ -6751,8 +7103,11 @@
       <c r="N116" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>251801117</v>
       </c>
@@ -6795,8 +7150,11 @@
       <c r="N117" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>251801118</v>
       </c>
@@ -6839,8 +7197,11 @@
       <c r="N118" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O118" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>251801119</v>
       </c>
@@ -6883,8 +7244,11 @@
       <c r="N119" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>251801120</v>
       </c>
@@ -6927,8 +7291,11 @@
       <c r="N120" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>251801122</v>
       </c>
@@ -6971,8 +7338,11 @@
       <c r="N121" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>251801123</v>
       </c>
@@ -7015,8 +7385,11 @@
       <c r="N122" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>251801124</v>
       </c>
@@ -7059,8 +7432,11 @@
       <c r="N123" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>251801125</v>
       </c>
@@ -7103,8 +7479,11 @@
       <c r="N124" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>251801126</v>
       </c>
@@ -7147,8 +7526,11 @@
       <c r="N125" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>251801127</v>
       </c>
@@ -7191,8 +7573,11 @@
       <c r="N126" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>251801128</v>
       </c>
@@ -7235,8 +7620,11 @@
       <c r="N127" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>251801129</v>
       </c>
@@ -7279,8 +7667,11 @@
       <c r="N128" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>251801130</v>
       </c>
@@ -7323,8 +7714,11 @@
       <c r="N129" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O129" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>251801131</v>
       </c>
@@ -7367,8 +7761,11 @@
       <c r="N130" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>251801132</v>
       </c>
@@ -7411,8 +7808,11 @@
       <c r="N131" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>251801133</v>
       </c>
@@ -7455,8 +7855,11 @@
       <c r="N132" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>251801134</v>
       </c>
@@ -7499,8 +7902,11 @@
       <c r="N133" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>251801135</v>
       </c>
@@ -7543,8 +7949,11 @@
       <c r="N134" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>251801136</v>
       </c>
@@ -7587,8 +7996,11 @@
       <c r="N135" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>251801137</v>
       </c>
@@ -7631,8 +8043,11 @@
       <c r="N136" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>251801138</v>
       </c>
@@ -7675,8 +8090,11 @@
       <c r="N137" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>251801139</v>
       </c>
@@ -7719,8 +8137,11 @@
       <c r="N138" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>251801140</v>
       </c>
@@ -7763,8 +8184,11 @@
       <c r="N139" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>251801141</v>
       </c>
@@ -7807,8 +8231,11 @@
       <c r="N140" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>251801142</v>
       </c>
@@ -7851,8 +8278,11 @@
       <c r="N141" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>251801143</v>
       </c>
@@ -7895,8 +8325,11 @@
       <c r="N142" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>251801144</v>
       </c>
@@ -7939,8 +8372,11 @@
       <c r="N143" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>251801145</v>
       </c>
@@ -7983,8 +8419,11 @@
       <c r="N144" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>251801146</v>
       </c>
@@ -8027,8 +8466,11 @@
       <c r="N145" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>251801147</v>
       </c>
@@ -8071,8 +8513,11 @@
       <c r="N146" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>251801148</v>
       </c>
@@ -8115,8 +8560,11 @@
       <c r="N147" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>251801149</v>
       </c>
@@ -8159,8 +8607,11 @@
       <c r="N148" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>251801150</v>
       </c>
@@ -8203,8 +8654,11 @@
       <c r="N149" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>251801151</v>
       </c>
@@ -8247,8 +8701,11 @@
       <c r="N150" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>251801152</v>
       </c>
@@ -8291,8 +8748,11 @@
       <c r="N151" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>251801153</v>
       </c>
@@ -8335,8 +8795,11 @@
       <c r="N152" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>251801154</v>
       </c>
@@ -8379,8 +8842,11 @@
       <c r="N153" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>251801155</v>
       </c>
@@ -8423,8 +8889,11 @@
       <c r="N154" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>251801156</v>
       </c>
@@ -8467,8 +8936,11 @@
       <c r="N155" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>251801157</v>
       </c>
@@ -8511,8 +8983,11 @@
       <c r="N156" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>251801158</v>
       </c>
@@ -8555,8 +9030,11 @@
       <c r="N157" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>251801159</v>
       </c>
@@ -8599,8 +9077,11 @@
       <c r="N158" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>251801160</v>
       </c>
@@ -8643,8 +9124,11 @@
       <c r="N159" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>251801161</v>
       </c>
@@ -8687,8 +9171,11 @@
       <c r="N160" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>251801162</v>
       </c>
@@ -8731,8 +9218,11 @@
       <c r="N161" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>251801163</v>
       </c>
@@ -8775,8 +9265,11 @@
       <c r="N162" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>251801164</v>
       </c>
@@ -8819,8 +9312,11 @@
       <c r="N163" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>251801165</v>
       </c>
@@ -8863,8 +9359,11 @@
       <c r="N164" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>251801166</v>
       </c>
@@ -8907,8 +9406,11 @@
       <c r="N165" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>251801167</v>
       </c>
@@ -8951,8 +9453,11 @@
       <c r="N166" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>251801168</v>
       </c>
@@ -8995,8 +9500,11 @@
       <c r="N167" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>251801169</v>
       </c>
@@ -9039,8 +9547,11 @@
       <c r="N168" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>251801170</v>
       </c>
@@ -9083,8 +9594,11 @@
       <c r="N169" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>251801171</v>
       </c>
@@ -9127,8 +9641,11 @@
       <c r="N170" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>251801172</v>
       </c>
@@ -9171,8 +9688,11 @@
       <c r="N171" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>251801173</v>
       </c>
@@ -9215,8 +9735,11 @@
       <c r="N172" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>251801174</v>
       </c>
@@ -9259,8 +9782,11 @@
       <c r="N173" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>251801175</v>
       </c>
@@ -9303,8 +9829,11 @@
       <c r="N174" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>251801176</v>
       </c>
@@ -9347,8 +9876,11 @@
       <c r="N175" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>251801177</v>
       </c>
@@ -9391,8 +9923,11 @@
       <c r="N176" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>251801178</v>
       </c>
@@ -9435,8 +9970,11 @@
       <c r="N177" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>251801179</v>
       </c>
@@ -9479,8 +10017,11 @@
       <c r="N178" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>251801180</v>
       </c>
@@ -9523,8 +10064,11 @@
       <c r="N179" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>251801181</v>
       </c>
@@ -9567,8 +10111,11 @@
       <c r="N180" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>251801182</v>
       </c>
@@ -9611,8 +10158,11 @@
       <c r="N181" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>251801183</v>
       </c>
@@ -9655,8 +10205,11 @@
       <c r="N182" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>251801184</v>
       </c>
@@ -9699,8 +10252,11 @@
       <c r="N183" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>251801185</v>
       </c>
@@ -9743,8 +10299,11 @@
       <c r="N184" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>251801186</v>
       </c>
@@ -9787,8 +10346,11 @@
       <c r="N185" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>251801187</v>
       </c>
@@ -9831,8 +10393,11 @@
       <c r="N186" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>251801188</v>
       </c>
@@ -9875,8 +10440,11 @@
       <c r="N187" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>251801189</v>
       </c>
@@ -9919,8 +10487,11 @@
       <c r="N188" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O188" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>251801190</v>
       </c>
@@ -9963,8 +10534,11 @@
       <c r="N189" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O189" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>251801191</v>
       </c>
@@ -10007,8 +10581,11 @@
       <c r="N190" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O190" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>251801192</v>
       </c>
@@ -10051,8 +10628,11 @@
       <c r="N191" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O191" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>251801193</v>
       </c>
@@ -10095,8 +10675,11 @@
       <c r="N192" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O192" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>251801194</v>
       </c>
@@ -10139,8 +10722,11 @@
       <c r="N193" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O193" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>251801195</v>
       </c>
@@ -10183,8 +10769,11 @@
       <c r="N194" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O194" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>251801196</v>
       </c>
@@ -10227,8 +10816,11 @@
       <c r="N195" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O195" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>251801197</v>
       </c>
@@ -10271,8 +10863,11 @@
       <c r="N196" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O196" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>251801198</v>
       </c>
@@ -10315,8 +10910,11 @@
       <c r="N197" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O197" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>251801199</v>
       </c>
@@ -10359,8 +10957,11 @@
       <c r="N198" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O198" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>251801200</v>
       </c>
@@ -10403,8 +11004,11 @@
       <c r="N199" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O199" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>251801202</v>
       </c>
@@ -10447,8 +11051,11 @@
       <c r="N200" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O200" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>251801203</v>
       </c>
@@ -10491,8 +11098,11 @@
       <c r="N201" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O201" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>251801204</v>
       </c>
@@ -10535,8 +11145,11 @@
       <c r="N202" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O202" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>251801205</v>
       </c>
@@ -10579,8 +11192,11 @@
       <c r="N203" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O203" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>251801206</v>
       </c>
@@ -10623,8 +11239,11 @@
       <c r="N204" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O204" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>251801207</v>
       </c>
@@ -10667,8 +11286,11 @@
       <c r="N205" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O205" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>251801208</v>
       </c>
@@ -10711,8 +11333,11 @@
       <c r="N206" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O206" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>251801209</v>
       </c>
@@ -10755,8 +11380,11 @@
       <c r="N207" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O207" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>251801210</v>
       </c>
@@ -10799,8 +11427,11 @@
       <c r="N208" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O208" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>251801211</v>
       </c>
@@ -10843,8 +11474,11 @@
       <c r="N209" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O209" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>251801212</v>
       </c>
@@ -10887,8 +11521,11 @@
       <c r="N210" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O210" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>251801213</v>
       </c>
@@ -10931,8 +11568,11 @@
       <c r="N211" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O211" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>251801214</v>
       </c>
@@ -10975,8 +11615,11 @@
       <c r="N212" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O212" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>251801215</v>
       </c>
@@ -11019,8 +11662,11 @@
       <c r="N213" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O213" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>251801216</v>
       </c>
@@ -11063,8 +11709,11 @@
       <c r="N214" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O214" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>251801217</v>
       </c>
@@ -11107,8 +11756,11 @@
       <c r="N215" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O215" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>251801218</v>
       </c>
@@ -11151,8 +11803,11 @@
       <c r="N216" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O216" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>251801219</v>
       </c>
@@ -11195,8 +11850,11 @@
       <c r="N217" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O217" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>251801220</v>
       </c>
@@ -11239,8 +11897,11 @@
       <c r="N218" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O218" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>251801221</v>
       </c>
@@ -11283,8 +11944,11 @@
       <c r="N219" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O219" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>251801223</v>
       </c>
@@ -11327,8 +11991,11 @@
       <c r="N220" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O220" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>251801224</v>
       </c>
@@ -11371,8 +12038,11 @@
       <c r="N221" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O221" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>251801225</v>
       </c>
@@ -11415,8 +12085,11 @@
       <c r="N222" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O222" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>251801226</v>
       </c>
@@ -11459,8 +12132,11 @@
       <c r="N223" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O223" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>251801227</v>
       </c>
@@ -11503,8 +12179,11 @@
       <c r="N224" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O224" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>251801228</v>
       </c>
@@ -11547,8 +12226,11 @@
       <c r="N225" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O225" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>251801229</v>
       </c>
@@ -11591,8 +12273,11 @@
       <c r="N226" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O226" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>251801230</v>
       </c>
@@ -11635,8 +12320,11 @@
       <c r="N227" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O227" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>251801231</v>
       </c>
@@ -11679,8 +12367,11 @@
       <c r="N228" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O228" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>251801233</v>
       </c>
@@ -11723,8 +12414,11 @@
       <c r="N229" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O229" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>251801234</v>
       </c>
@@ -11767,8 +12461,11 @@
       <c r="N230" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O230" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>251801235</v>
       </c>
@@ -11811,8 +12508,11 @@
       <c r="N231" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O231" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>251801236</v>
       </c>
@@ -11855,8 +12555,11 @@
       <c r="N232" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O232" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>251801237</v>
       </c>
@@ -11899,8 +12602,11 @@
       <c r="N233" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O233" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>251801238</v>
       </c>
@@ -11943,8 +12649,11 @@
       <c r="N234" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O234" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>251801239</v>
       </c>
@@ -11987,8 +12696,11 @@
       <c r="N235" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O235" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>251801240</v>
       </c>
@@ -12031,8 +12743,11 @@
       <c r="N236" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O236" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>251801241</v>
       </c>
@@ -12075,8 +12790,11 @@
       <c r="N237" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O237" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>251801242</v>
       </c>
@@ -12119,8 +12837,11 @@
       <c r="N238" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O238" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>251801243</v>
       </c>
@@ -12163,8 +12884,11 @@
       <c r="N239" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O239" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>251801244</v>
       </c>
@@ -12207,8 +12931,11 @@
       <c r="N240" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O240" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>251801245</v>
       </c>
@@ -12251,8 +12978,11 @@
       <c r="N241" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O241" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>251801246</v>
       </c>
@@ -12295,8 +13025,11 @@
       <c r="N242" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O242" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>251801247</v>
       </c>
@@ -12339,8 +13072,11 @@
       <c r="N243" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O243" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>251801248</v>
       </c>
@@ -12383,8 +13119,11 @@
       <c r="N244" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O244" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>251801249</v>
       </c>
@@ -12427,8 +13166,11 @@
       <c r="N245" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O245" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>251801250</v>
       </c>
@@ -12471,8 +13213,11 @@
       <c r="N246" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O246" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>251801251</v>
       </c>
@@ -12515,8 +13260,11 @@
       <c r="N247" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O247" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>251801252</v>
       </c>
@@ -12559,8 +13307,11 @@
       <c r="N248" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O248" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>251801253</v>
       </c>
@@ -12603,8 +13354,11 @@
       <c r="N249" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O249" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>251801254</v>
       </c>
@@ -12647,8 +13401,11 @@
       <c r="N250" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O250" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>251801255</v>
       </c>
@@ -12691,8 +13448,11 @@
       <c r="N251" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O251" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>251801256</v>
       </c>
@@ -12735,8 +13495,11 @@
       <c r="N252" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O252" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>251801257</v>
       </c>
@@ -12779,8 +13542,11 @@
       <c r="N253" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O253" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>251801258</v>
       </c>
@@ -12823,8 +13589,11 @@
       <c r="N254" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O254" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>251801259</v>
       </c>
@@ -12867,8 +13636,11 @@
       <c r="N255" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O255" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>251801260</v>
       </c>
@@ -12911,8 +13683,11 @@
       <c r="N256" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O256" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>251801261</v>
       </c>
@@ -12955,8 +13730,11 @@
       <c r="N257" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O257" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>251801262</v>
       </c>
@@ -12999,8 +13777,11 @@
       <c r="N258" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O258" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>251801263</v>
       </c>
@@ -13043,8 +13824,11 @@
       <c r="N259" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O259" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>251801264</v>
       </c>
@@ -13087,8 +13871,11 @@
       <c r="N260" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O260" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>251801265</v>
       </c>
@@ -13131,8 +13918,11 @@
       <c r="N261" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O261" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>251801266</v>
       </c>
@@ -13175,8 +13965,11 @@
       <c r="N262" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O262" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>251801268</v>
       </c>
@@ -13219,8 +14012,11 @@
       <c r="N263" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O263" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>251801269</v>
       </c>
@@ -13263,8 +14059,11 @@
       <c r="N264" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O264" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>251801270</v>
       </c>
@@ -13307,8 +14106,11 @@
       <c r="N265" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O265" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>251801271</v>
       </c>
@@ -13351,8 +14153,11 @@
       <c r="N266" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O266" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>251801272</v>
       </c>
@@ -13395,8 +14200,11 @@
       <c r="N267" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O267" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>251801273</v>
       </c>
@@ -13439,8 +14247,11 @@
       <c r="N268" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O268" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>251801274</v>
       </c>
@@ -13483,8 +14294,11 @@
       <c r="N269" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O269" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>251801275</v>
       </c>
@@ -13527,8 +14341,11 @@
       <c r="N270" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O270" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>251801276</v>
       </c>
@@ -13571,8 +14388,11 @@
       <c r="N271" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O271" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>251801277</v>
       </c>
@@ -13615,8 +14435,11 @@
       <c r="N272" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O272" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>251801278</v>
       </c>
@@ -13659,8 +14482,11 @@
       <c r="N273" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O273" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>251801279</v>
       </c>
@@ -13703,8 +14529,11 @@
       <c r="N274" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O274" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>251801280</v>
       </c>
@@ -13747,8 +14576,11 @@
       <c r="N275" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O275" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>251801281</v>
       </c>
@@ -13791,8 +14623,11 @@
       <c r="N276" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O276" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>251801282</v>
       </c>
@@ -13835,8 +14670,11 @@
       <c r="N277" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O277" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>251801283</v>
       </c>
@@ -13879,8 +14717,11 @@
       <c r="N278" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O278" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>251801285</v>
       </c>
@@ -13923,8 +14764,11 @@
       <c r="N279" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O279" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>251801286</v>
       </c>
@@ -13967,8 +14811,11 @@
       <c r="N280" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O280" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>251801287</v>
       </c>
@@ -14011,8 +14858,11 @@
       <c r="N281" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O281" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>251801288</v>
       </c>
@@ -14055,8 +14905,11 @@
       <c r="N282" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O282" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>251801289</v>
       </c>
@@ -14099,8 +14952,11 @@
       <c r="N283" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O283" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>251801290</v>
       </c>
@@ -14143,8 +14999,11 @@
       <c r="N284" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O284" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>251801291</v>
       </c>
@@ -14187,8 +15046,11 @@
       <c r="N285" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O285" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>251801292</v>
       </c>
@@ -14231,8 +15093,11 @@
       <c r="N286" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O286" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>251801293</v>
       </c>
@@ -14275,8 +15140,11 @@
       <c r="N287" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O287" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>251801294</v>
       </c>
@@ -14319,8 +15187,11 @@
       <c r="N288" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O288" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>251801295</v>
       </c>
@@ -14363,8 +15234,11 @@
       <c r="N289" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O289" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>251801296</v>
       </c>
@@ -14407,8 +15281,11 @@
       <c r="N290" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O290" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>251801297</v>
       </c>
@@ -14451,8 +15328,11 @@
       <c r="N291" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O291" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>251801298</v>
       </c>
@@ -14495,8 +15375,11 @@
       <c r="N292" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O292" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>251801299</v>
       </c>
@@ -14539,8 +15422,11 @@
       <c r="N293" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O293" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>251801300</v>
       </c>
@@ -14583,8 +15469,11 @@
       <c r="N294" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O294" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>251801301</v>
       </c>
@@ -14627,8 +15516,11 @@
       <c r="N295" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O295" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>251801302</v>
       </c>
@@ -14671,8 +15563,11 @@
       <c r="N296" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O296" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>251801303</v>
       </c>
@@ -14715,8 +15610,11 @@
       <c r="N297" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O297" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>251801304</v>
       </c>
@@ -14759,8 +15657,11 @@
       <c r="N298" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O298" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>251801305</v>
       </c>
@@ -14803,8 +15704,11 @@
       <c r="N299" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O299" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>251801306</v>
       </c>
@@ -14847,8 +15751,11 @@
       <c r="N300" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O300" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>251801307</v>
       </c>
@@ -14891,8 +15798,11 @@
       <c r="N301" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O301" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>251801308</v>
       </c>
@@ -14935,8 +15845,11 @@
       <c r="N302" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O302" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>251801309</v>
       </c>
@@ -14979,8 +15892,11 @@
       <c r="N303" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O303" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>251801310</v>
       </c>
@@ -15023,8 +15939,11 @@
       <c r="N304" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O304" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>251801311</v>
       </c>
@@ -15067,8 +15986,11 @@
       <c r="N305" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O305" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>251801312</v>
       </c>
@@ -15111,8 +16033,11 @@
       <c r="N306" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O306" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>251801313</v>
       </c>
@@ -15155,8 +16080,11 @@
       <c r="N307" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O307" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>251801314</v>
       </c>
@@ -15199,8 +16127,11 @@
       <c r="N308" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O308" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>251801315</v>
       </c>
@@ -15243,8 +16174,11 @@
       <c r="N309" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O309" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>251801316</v>
       </c>
@@ -15287,8 +16221,11 @@
       <c r="N310" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O310" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>251801317</v>
       </c>
@@ -15331,8 +16268,11 @@
       <c r="N311" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O311" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>251801318</v>
       </c>
@@ -15375,8 +16315,11 @@
       <c r="N312" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O312" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>251801319</v>
       </c>
@@ -15419,8 +16362,11 @@
       <c r="N313" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O313" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>251801320</v>
       </c>
@@ -15463,8 +16409,11 @@
       <c r="N314" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O314" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>251801322</v>
       </c>
@@ -15507,8 +16456,11 @@
       <c r="N315" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O315" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>251801323</v>
       </c>
@@ -15551,8 +16503,11 @@
       <c r="N316" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O316" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>251801324</v>
       </c>
@@ -15595,8 +16550,11 @@
       <c r="N317" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O317" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>251801325</v>
       </c>
@@ -15639,8 +16597,11 @@
       <c r="N318" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O318" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>251801326</v>
       </c>
@@ -15683,8 +16644,11 @@
       <c r="N319" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O319" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>251801327</v>
       </c>
@@ -15727,8 +16691,11 @@
       <c r="N320" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O320" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>251801328</v>
       </c>
@@ -15771,8 +16738,11 @@
       <c r="N321" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O321" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>251801329</v>
       </c>
@@ -15815,8 +16785,11 @@
       <c r="N322" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O322" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>251801330</v>
       </c>
@@ -15859,8 +16832,11 @@
       <c r="N323" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O323" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>251801331</v>
       </c>
@@ -15903,8 +16879,11 @@
       <c r="N324" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O324" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>251801332</v>
       </c>
@@ -15947,8 +16926,11 @@
       <c r="N325" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O325" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>251801333</v>
       </c>
@@ -15991,8 +16973,11 @@
       <c r="N326" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O326" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>251801334</v>
       </c>
@@ -16035,8 +17020,11 @@
       <c r="N327" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O327" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>251801335</v>
       </c>
@@ -16079,8 +17067,11 @@
       <c r="N328" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O328" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>251801336</v>
       </c>
@@ -16123,8 +17114,11 @@
       <c r="N329" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O329" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>251801337</v>
       </c>
@@ -16167,8 +17161,11 @@
       <c r="N330" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O330" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>251801338</v>
       </c>
@@ -16211,8 +17208,11 @@
       <c r="N331" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O331" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>251801339</v>
       </c>
@@ -16255,8 +17255,11 @@
       <c r="N332" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O332" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>251801340</v>
       </c>
@@ -16299,8 +17302,11 @@
       <c r="N333" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O333" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>251801341</v>
       </c>
@@ -16343,8 +17349,11 @@
       <c r="N334" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O334" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>251801342</v>
       </c>
@@ -16387,8 +17396,11 @@
       <c r="N335" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O335" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>251801343</v>
       </c>
@@ -16431,8 +17443,11 @@
       <c r="N336" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O336" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>251801344</v>
       </c>
@@ -16475,8 +17490,11 @@
       <c r="N337" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O337" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>251801345</v>
       </c>
@@ -16519,8 +17537,11 @@
       <c r="N338" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O338" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>251801346</v>
       </c>
@@ -16563,8 +17584,11 @@
       <c r="N339" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O339" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>251801347</v>
       </c>
@@ -16607,8 +17631,11 @@
       <c r="N340" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O340" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>251801348</v>
       </c>
@@ -16651,8 +17678,11 @@
       <c r="N341" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O341" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>251801349</v>
       </c>
@@ -16695,8 +17725,11 @@
       <c r="N342" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O342" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>251801350</v>
       </c>
@@ -16739,8 +17772,11 @@
       <c r="N343" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O343" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>251801351</v>
       </c>
@@ -16783,8 +17819,11 @@
       <c r="N344" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O344" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>251801352</v>
       </c>
@@ -16827,8 +17866,11 @@
       <c r="N345" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O345" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>251801353</v>
       </c>
@@ -16871,8 +17913,11 @@
       <c r="N346" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O346" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>251801354</v>
       </c>
@@ -16915,8 +17960,11 @@
       <c r="N347" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O347" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>251801355</v>
       </c>
@@ -16959,8 +18007,11 @@
       <c r="N348" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O348" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>251801356</v>
       </c>
@@ -17003,8 +18054,11 @@
       <c r="N349" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O349" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>251801357</v>
       </c>
@@ -17047,8 +18101,11 @@
       <c r="N350" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O350" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>251801358</v>
       </c>
@@ -17091,8 +18148,11 @@
       <c r="N351" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O351" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>251801359</v>
       </c>
@@ -17135,8 +18195,11 @@
       <c r="N352" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O352" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>251801360</v>
       </c>
@@ -17179,8 +18242,11 @@
       <c r="N353" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O353" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>251801361</v>
       </c>
@@ -17223,8 +18289,11 @@
       <c r="N354" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O354" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>251801362</v>
       </c>
@@ -17267,8 +18336,11 @@
       <c r="N355" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O355" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>251801363</v>
       </c>
@@ -17311,8 +18383,11 @@
       <c r="N356" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O356" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>251801364</v>
       </c>
@@ -17355,8 +18430,11 @@
       <c r="N357" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O357" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>251801365</v>
       </c>
@@ -17399,8 +18477,11 @@
       <c r="N358" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O358" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>251801366</v>
       </c>
@@ -17443,8 +18524,11 @@
       <c r="N359" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O359" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>251801367</v>
       </c>
@@ -17487,8 +18571,11 @@
       <c r="N360" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O360" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>251801368</v>
       </c>
@@ -17531,8 +18618,11 @@
       <c r="N361" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O361" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>251801369</v>
       </c>
@@ -17575,8 +18665,11 @@
       <c r="N362" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O362" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>251801370</v>
       </c>
@@ -17619,8 +18712,11 @@
       <c r="N363" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O363" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>251801371</v>
       </c>
@@ -17663,8 +18759,11 @@
       <c r="N364" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O364" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>251801372</v>
       </c>
@@ -17707,8 +18806,11 @@
       <c r="N365" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O365" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>251801373</v>
       </c>
@@ -17751,8 +18853,11 @@
       <c r="N366" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O366" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>251801374</v>
       </c>
@@ -17795,8 +18900,11 @@
       <c r="N367" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O367" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>251801375</v>
       </c>
@@ -17839,8 +18947,11 @@
       <c r="N368" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O368" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>251801377</v>
       </c>
@@ -17883,8 +18994,11 @@
       <c r="N369" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O369" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>251801378</v>
       </c>
@@ -17927,8 +19041,11 @@
       <c r="N370" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O370" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>251801379</v>
       </c>
@@ -17971,8 +19088,11 @@
       <c r="N371" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O371" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>251801380</v>
       </c>
@@ -18015,8 +19135,11 @@
       <c r="N372" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O372" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>251801381</v>
       </c>
@@ -18059,8 +19182,11 @@
       <c r="N373" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O373" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>251801382</v>
       </c>
@@ -18103,8 +19229,11 @@
       <c r="N374" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O374" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>251801383</v>
       </c>
@@ -18147,8 +19276,11 @@
       <c r="N375" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O375" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>251801384</v>
       </c>
@@ -18191,8 +19323,11 @@
       <c r="N376" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O376" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>251801385</v>
       </c>
@@ -18235,8 +19370,11 @@
       <c r="N377" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O377" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>251801386</v>
       </c>
@@ -18279,8 +19417,11 @@
       <c r="N378" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O378" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>251801387</v>
       </c>
@@ -18323,8 +19464,11 @@
       <c r="N379" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O379" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>251801388</v>
       </c>
@@ -18367,8 +19511,11 @@
       <c r="N380" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O380" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>251801389</v>
       </c>
@@ -18411,8 +19558,11 @@
       <c r="N381" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O381" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>251801391</v>
       </c>
@@ -18455,8 +19605,11 @@
       <c r="N382" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O382" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>251801392</v>
       </c>
@@ -18499,8 +19652,11 @@
       <c r="N383" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O383" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>251801393</v>
       </c>
@@ -18543,8 +19699,11 @@
       <c r="N384" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O384" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>251801394</v>
       </c>
@@ -18587,8 +19746,11 @@
       <c r="N385" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O385" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>251801395</v>
       </c>
@@ -18631,8 +19793,11 @@
       <c r="N386" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O386" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>251801501</v>
       </c>
@@ -18675,8 +19840,11 @@
       <c r="N387" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O387" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>251801502</v>
       </c>
@@ -18719,8 +19887,11 @@
       <c r="N388" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O388" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>251801503</v>
       </c>
@@ -18763,8 +19934,11 @@
       <c r="N389" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O389" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>251801504</v>
       </c>
@@ -18807,8 +19981,11 @@
       <c r="N390" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O390" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>251801505</v>
       </c>
@@ -18851,8 +20028,11 @@
       <c r="N391" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O391" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>251801506</v>
       </c>
@@ -18895,8 +20075,11 @@
       <c r="N392" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O392" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>251801507</v>
       </c>
@@ -18939,8 +20122,11 @@
       <c r="N393" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O393" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>251801508</v>
       </c>
@@ -18983,8 +20169,11 @@
       <c r="N394" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O394" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>251801509</v>
       </c>
@@ -19027,8 +20216,11 @@
       <c r="N395" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O395" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>251801510</v>
       </c>
@@ -19071,8 +20263,11 @@
       <c r="N396" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O396" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>251801511</v>
       </c>
@@ -19115,8 +20310,11 @@
       <c r="N397" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O397" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>251801512</v>
       </c>
@@ -19159,8 +20357,11 @@
       <c r="N398" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O398" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>251801513</v>
       </c>
@@ -19203,8 +20404,11 @@
       <c r="N399" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O399" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>251801514</v>
       </c>
@@ -19247,8 +20451,11 @@
       <c r="N400" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O400" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>251801515</v>
       </c>
@@ -19291,8 +20498,11 @@
       <c r="N401" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O401" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>251801701</v>
       </c>
@@ -19335,8 +20545,11 @@
       <c r="N402" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O402" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>251801901</v>
       </c>
@@ -19379,8 +20592,12 @@
       <c r="N403" s="2">
         <v>26</v>
       </c>
+      <c r="O403" s="2" t="s">
+        <v>415</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/PTM/2026_PTM_SecondYr_data.xlsx
+++ b/PTM/2026_PTM_SecondYr_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026_Even\WTMA\WTMA_LAB\WTMA-Lab\PTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12220ED2-E9AC-4435-8B9B-A0456D94EB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4B581C-2181-4138-B6AC-25D3B506BDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="616">
   <si>
     <t>Registration Id</t>
   </si>
@@ -1272,12 +1272,6 @@
     <t>Environmental Science and Engineering-M</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>No Of Arrearss</t>
-  </si>
-  <si>
     <t>ABSENT</t>
   </si>
   <si>
@@ -1285,6 +1279,600 @@
   </si>
   <si>
     <t>Mal Practice</t>
+  </si>
+  <si>
+    <t>8.36</t>
+  </si>
+  <si>
+    <t>2.68</t>
+  </si>
+  <si>
+    <t>8.07</t>
+  </si>
+  <si>
+    <t>8.39</t>
+  </si>
+  <si>
+    <t>6.86</t>
+  </si>
+  <si>
+    <t>5.14</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>6.61</t>
+  </si>
+  <si>
+    <t>7.95</t>
+  </si>
+  <si>
+    <t>6.09</t>
+  </si>
+  <si>
+    <t>4.09</t>
+  </si>
+  <si>
+    <t>4.18</t>
+  </si>
+  <si>
+    <t>7.23</t>
+  </si>
+  <si>
+    <t>3.50</t>
+  </si>
+  <si>
+    <t>9.05</t>
+  </si>
+  <si>
+    <t>5.73</t>
+  </si>
+  <si>
+    <t>2.09</t>
+  </si>
+  <si>
+    <t>9.00</t>
+  </si>
+  <si>
+    <t>5.32</t>
+  </si>
+  <si>
+    <t>8.45</t>
+  </si>
+  <si>
+    <t>4.34</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>5.50</t>
+  </si>
+  <si>
+    <t>8.05</t>
+  </si>
+  <si>
+    <t>4.05</t>
+  </si>
+  <si>
+    <t>4.43</t>
+  </si>
+  <si>
+    <t>8.59</t>
+  </si>
+  <si>
+    <t>5.70</t>
+  </si>
+  <si>
+    <t>2.77</t>
+  </si>
+  <si>
+    <t>7.98</t>
+  </si>
+  <si>
+    <t>3.55</t>
+  </si>
+  <si>
+    <t>7.48</t>
+  </si>
+  <si>
+    <t>7.68</t>
+  </si>
+  <si>
+    <t>9.18</t>
+  </si>
+  <si>
+    <t>8.77</t>
+  </si>
+  <si>
+    <t>5.82</t>
+  </si>
+  <si>
+    <t>3.18</t>
+  </si>
+  <si>
+    <t>8.55</t>
+  </si>
+  <si>
+    <t>5.59</t>
+  </si>
+  <si>
+    <t>8.64</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>7.70</t>
+  </si>
+  <si>
+    <t>9.50</t>
+  </si>
+  <si>
+    <t>7.59</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>2.73</t>
+  </si>
+  <si>
+    <t>9.23</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>1.73</t>
+  </si>
+  <si>
+    <t>8.50</t>
+  </si>
+  <si>
+    <t>8.86</t>
+  </si>
+  <si>
+    <t>7.82</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>9.95</t>
+  </si>
+  <si>
+    <t>6.91</t>
+  </si>
+  <si>
+    <t>2.48</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>9.55</t>
+  </si>
+  <si>
+    <t>4.64</t>
+  </si>
+  <si>
+    <t>8.09</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>4.80</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>6.43</t>
+  </si>
+  <si>
+    <t>9.27</t>
+  </si>
+  <si>
+    <t>7.75</t>
+  </si>
+  <si>
+    <t>8.68</t>
+  </si>
+  <si>
+    <t>7.43</t>
+  </si>
+  <si>
+    <t>7.07</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>4.95</t>
+  </si>
+  <si>
+    <t>7.39</t>
+  </si>
+  <si>
+    <t>8.14</t>
+  </si>
+  <si>
+    <t>8.27</t>
+  </si>
+  <si>
+    <t>9.73</t>
+  </si>
+  <si>
+    <t>7.91</t>
+  </si>
+  <si>
+    <t>8.18</t>
+  </si>
+  <si>
+    <t>9.86</t>
+  </si>
+  <si>
+    <t>8.41</t>
+  </si>
+  <si>
+    <t>2.64</t>
+  </si>
+  <si>
+    <t>7.34</t>
+  </si>
+  <si>
+    <t>6.00</t>
+  </si>
+  <si>
+    <t>8.23</t>
+  </si>
+  <si>
+    <t>5.36</t>
+  </si>
+  <si>
+    <t>9.36</t>
+  </si>
+  <si>
+    <t>7.73</t>
+  </si>
+  <si>
+    <t>8.95</t>
+  </si>
+  <si>
+    <t>4.16</t>
+  </si>
+  <si>
+    <t>6.14</t>
+  </si>
+  <si>
+    <t>5.18</t>
+  </si>
+  <si>
+    <t>8.16</t>
+  </si>
+  <si>
+    <t>7.09</t>
+  </si>
+  <si>
+    <t>7.86</t>
+  </si>
+  <si>
+    <t>6.18</t>
+  </si>
+  <si>
+    <t>4.32</t>
+  </si>
+  <si>
+    <t>5.00</t>
+  </si>
+  <si>
+    <t>8.82</t>
+  </si>
+  <si>
+    <t>6.95</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>5.68</t>
+  </si>
+  <si>
+    <t>5.61</t>
+  </si>
+  <si>
+    <t>4.39</t>
+  </si>
+  <si>
+    <t>7.20</t>
+  </si>
+  <si>
+    <t>9.32</t>
+  </si>
+  <si>
+    <t>5.41</t>
+  </si>
+  <si>
+    <t>6.80</t>
+  </si>
+  <si>
+    <t>7.14</t>
+  </si>
+  <si>
+    <t>2.86</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>7.55</t>
+  </si>
+  <si>
+    <t>8.66</t>
+  </si>
+  <si>
+    <t>8.34</t>
+  </si>
+  <si>
+    <t>5.91</t>
+  </si>
+  <si>
+    <t>8.73</t>
+  </si>
+  <si>
+    <t>6.64</t>
+  </si>
+  <si>
+    <t>1.52</t>
+  </si>
+  <si>
+    <t>8.57</t>
+  </si>
+  <si>
+    <t>8.00</t>
+  </si>
+  <si>
+    <t>6.45</t>
+  </si>
+  <si>
+    <t>4.82</t>
+  </si>
+  <si>
+    <t>2.43</t>
+  </si>
+  <si>
+    <t>4.07</t>
+  </si>
+  <si>
+    <t>7.77</t>
+  </si>
+  <si>
+    <t>3.20</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>9.14</t>
+  </si>
+  <si>
+    <t>7.64</t>
+  </si>
+  <si>
+    <t>6.73</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>6.68</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>3.25</t>
+  </si>
+  <si>
+    <t>8.11</t>
+  </si>
+  <si>
+    <t>3.66</t>
+  </si>
+  <si>
+    <t>7.00</t>
+  </si>
+  <si>
+    <t>7.41</t>
+  </si>
+  <si>
+    <t>2.80</t>
+  </si>
+  <si>
+    <t>7.36</t>
+  </si>
+  <si>
+    <t>4.50</t>
+  </si>
+  <si>
+    <t>3.86</t>
+  </si>
+  <si>
+    <t>8.91</t>
+  </si>
+  <si>
+    <t>3.77</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>3.75</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>2.23</t>
+  </si>
+  <si>
+    <t>4.23</t>
+  </si>
+  <si>
+    <t>7.32</t>
+  </si>
+  <si>
+    <t>3.59</t>
+  </si>
+  <si>
+    <t>1.55</t>
+  </si>
+  <si>
+    <t>3.82</t>
+  </si>
+  <si>
+    <t>6.36</t>
+  </si>
+  <si>
+    <t>1.61</t>
+  </si>
+  <si>
+    <t>5.89</t>
+  </si>
+  <si>
+    <t>3.91</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>4.14</t>
+  </si>
+  <si>
+    <t>4.86</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>3.32</t>
+  </si>
+  <si>
+    <t>5.93</t>
+  </si>
+  <si>
+    <t>6.39</t>
+  </si>
+  <si>
+    <t>5.48</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>3.48</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>5.39</t>
+  </si>
+  <si>
+    <t>6.23</t>
+  </si>
+  <si>
+    <t>9.77</t>
+  </si>
+  <si>
+    <t>9.09</t>
+  </si>
+  <si>
+    <t>5.02</t>
+  </si>
+  <si>
+    <t>5.75</t>
+  </si>
+  <si>
+    <t>5.55</t>
+  </si>
+  <si>
+    <t>5.77</t>
+  </si>
+  <si>
+    <t>5.86</t>
+  </si>
+  <si>
+    <t>5.27</t>
+  </si>
+  <si>
+    <t>9.41</t>
+  </si>
+  <si>
+    <t>7.93</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>7.30</t>
+  </si>
+  <si>
+    <t>4.27</t>
+  </si>
+  <si>
+    <t>5.09</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t>5.95</t>
+  </si>
+  <si>
+    <t>6.55</t>
+  </si>
+  <si>
+    <t>7.45</t>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <t>9.45</t>
+  </si>
+  <si>
+    <t>4.25</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>3.57</t>
+  </si>
+  <si>
+    <t>3.45</t>
+  </si>
+  <si>
+    <t>Lateral Entry</t>
+  </si>
+  <si>
+    <t>No Of Arrears</t>
+  </si>
+  <si>
+    <t>GPA</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1882,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1327,6 +1915,17 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1336,7 +1935,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1359,11 +1958,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1392,6 +2004,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1673,7 +2309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O403"/>
+  <dimension ref="A1:P403"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1689,10 +2325,11 @@
     <col min="13" max="13" width="38.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="44" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="2"/>
+    <col min="16" max="16" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1736,10 +2373,13 @@
         <v>414</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>251801001</v>
       </c>
@@ -1782,11 +2422,14 @@
       <c r="N2" s="9">
         <v>40</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O2" s="11">
+        <v>0</v>
+      </c>
+      <c r="P2" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>251801002</v>
       </c>
@@ -1829,11 +2472,14 @@
       <c r="N3" s="9">
         <v>66</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O3" s="11">
+        <v>5</v>
+      </c>
+      <c r="P3" s="11">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>251801003</v>
       </c>
@@ -1876,11 +2522,14 @@
       <c r="N4" s="9">
         <v>50</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O4" s="11">
+        <v>2</v>
+      </c>
+      <c r="P4" s="11">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>251801004</v>
       </c>
@@ -1923,11 +2572,14 @@
       <c r="N5" s="9">
         <v>44</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11">
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>251801005</v>
       </c>
@@ -1970,11 +2622,14 @@
       <c r="N6" s="9">
         <v>65</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="11">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>251801006</v>
       </c>
@@ -2017,11 +2672,14 @@
       <c r="N7" s="9">
         <v>68</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O7" s="11">
+        <v>1</v>
+      </c>
+      <c r="P7" s="11">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>251801007</v>
       </c>
@@ -2064,11 +2722,14 @@
       <c r="N8" s="9">
         <v>46</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O8" s="11">
+        <v>3</v>
+      </c>
+      <c r="P8" s="11">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>251801008</v>
       </c>
@@ -2111,11 +2772,14 @@
       <c r="N9" s="9">
         <v>44</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O9" s="11">
+        <v>3</v>
+      </c>
+      <c r="P9" s="11">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>251801009</v>
       </c>
@@ -2150,7 +2814,7 @@
         <v>78.459999999999994</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M10" s="7">
         <v>94.74</v>
@@ -2158,11 +2822,14 @@
       <c r="N10" s="9">
         <v>61</v>
       </c>
-      <c r="O10" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O10" s="11">
+        <v>1</v>
+      </c>
+      <c r="P10" s="11">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>251801010</v>
       </c>
@@ -2205,11 +2872,14 @@
       <c r="N11" s="9">
         <v>38</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O11" s="11">
+        <v>2</v>
+      </c>
+      <c r="P11" s="11">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>251801011</v>
       </c>
@@ -2252,11 +2922,14 @@
       <c r="N12" s="9">
         <v>60</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O12" s="11">
+        <v>1</v>
+      </c>
+      <c r="P12" s="11">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>251801012</v>
       </c>
@@ -2299,11 +2972,14 @@
       <c r="N13" s="9">
         <v>38</v>
       </c>
-      <c r="O13" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O13" s="11">
+        <v>1</v>
+      </c>
+      <c r="P13" s="11">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>251801013</v>
       </c>
@@ -2346,11 +3022,14 @@
       <c r="N14" s="9">
         <v>57</v>
       </c>
-      <c r="O14" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O14" s="11">
+        <v>0</v>
+      </c>
+      <c r="P14" s="11">
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>251801014</v>
       </c>
@@ -2393,11 +3072,14 @@
       <c r="N15" s="9">
         <v>54</v>
       </c>
-      <c r="O15" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O15" s="11">
+        <v>2</v>
+      </c>
+      <c r="P15" s="11">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>251801015</v>
       </c>
@@ -2438,13 +3120,16 @@
         <v>100</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="O16" s="2" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O16" s="11">
+        <v>0</v>
+      </c>
+      <c r="P16" s="11">
+        <v>8.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>251801016</v>
       </c>
@@ -2455,7 +3140,7 @@
         <v>90.91</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E17" s="7">
         <v>91.94</v>
@@ -2487,11 +3172,14 @@
       <c r="N17" s="9">
         <v>47</v>
       </c>
-      <c r="O17" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O17" s="11">
+        <v>2</v>
+      </c>
+      <c r="P17" s="11">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>251801017</v>
       </c>
@@ -2514,13 +3202,13 @@
         <v>93.24</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I18" s="7">
         <v>91.43</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K18" s="7">
         <v>88.06</v>
@@ -2534,11 +3222,14 @@
       <c r="N18" s="9">
         <v>70</v>
       </c>
-      <c r="O18" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O18" s="11">
+        <v>1</v>
+      </c>
+      <c r="P18" s="11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>251801018</v>
       </c>
@@ -2581,11 +3272,14 @@
       <c r="N19" s="9">
         <v>54</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O19" s="11">
+        <v>1</v>
+      </c>
+      <c r="P19" s="11">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>251801019</v>
       </c>
@@ -2628,11 +3322,14 @@
       <c r="N20" s="9">
         <v>69</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O20" s="11">
+        <v>1</v>
+      </c>
+      <c r="P20" s="11">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>251801020</v>
       </c>
@@ -2643,7 +3340,7 @@
         <v>74.650000000000006</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E21" s="7">
         <v>83.67</v>
@@ -2667,7 +3364,7 @@
         <v>79.099999999999994</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M21" s="7">
         <v>88.89</v>
@@ -2675,11 +3372,14 @@
       <c r="N21" s="9">
         <v>49</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O21" s="11">
+        <v>1</v>
+      </c>
+      <c r="P21" s="11">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>251801021</v>
       </c>
@@ -2722,11 +3422,14 @@
       <c r="N22" s="9">
         <v>68</v>
       </c>
-      <c r="O22" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O22" s="11">
+        <v>1</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>251801022</v>
       </c>
@@ -2769,11 +3472,14 @@
       <c r="N23" s="9">
         <v>70</v>
       </c>
-      <c r="O23" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O23" s="11">
+        <v>3</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>251801023</v>
       </c>
@@ -2816,11 +3522,14 @@
       <c r="N24" s="9">
         <v>49</v>
       </c>
-      <c r="O24" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O24" s="11">
+        <v>0</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>251801024</v>
       </c>
@@ -2863,11 +3572,14 @@
       <c r="N25" s="9">
         <v>49</v>
       </c>
-      <c r="O25" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O25" s="11">
+        <v>0</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>251801025</v>
       </c>
@@ -2910,11 +3622,14 @@
       <c r="N26" s="9">
         <v>60</v>
       </c>
-      <c r="O26" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O26" s="11">
+        <v>0</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>251801026</v>
       </c>
@@ -2957,11 +3672,14 @@
       <c r="N27" s="9">
         <v>38</v>
       </c>
-      <c r="O27" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O27" s="13">
+        <v>2</v>
+      </c>
+      <c r="P27" s="14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>251801027</v>
       </c>
@@ -2972,7 +3690,7 @@
         <v>90.91</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E28" s="8">
         <v>88.71</v>
@@ -3004,11 +3722,14 @@
       <c r="N28" s="9">
         <v>38</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O28" s="11">
+        <v>7</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>251801028</v>
       </c>
@@ -3051,11 +3772,14 @@
       <c r="N29" s="9">
         <v>51</v>
       </c>
-      <c r="O29" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O29" s="11">
+        <v>1</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>251801029</v>
       </c>
@@ -3098,11 +3822,14 @@
       <c r="N30" s="9">
         <v>46</v>
       </c>
-      <c r="O30" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O30" s="11">
+        <v>0</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>251801030</v>
       </c>
@@ -3145,11 +3872,14 @@
       <c r="N31" s="9">
         <v>71</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O31" s="11">
+        <v>1</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>251801031</v>
       </c>
@@ -3192,11 +3922,14 @@
       <c r="N32" s="9">
         <v>47</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O32" s="15">
+        <v>2</v>
+      </c>
+      <c r="P32" s="16" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>251801032</v>
       </c>
@@ -3219,7 +3952,7 @@
         <v>83.33</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I33" s="7">
         <v>93.75</v>
@@ -3239,11 +3972,14 @@
       <c r="N33" s="9">
         <v>55</v>
       </c>
-      <c r="O33" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O33" s="11">
+        <v>3</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>251801033</v>
       </c>
@@ -3286,11 +4022,14 @@
       <c r="N34" s="9">
         <v>46</v>
       </c>
-      <c r="O34" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O34" s="11">
+        <v>0</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>251801034</v>
       </c>
@@ -3333,11 +4072,14 @@
       <c r="N35" s="9">
         <v>56</v>
       </c>
-      <c r="O35" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O35" s="11">
+        <v>3</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>251801035</v>
       </c>
@@ -3380,11 +4122,14 @@
       <c r="N36" s="9">
         <v>51</v>
       </c>
-      <c r="O36" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O36" s="11">
+        <v>0</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>251801036</v>
       </c>
@@ -3427,11 +4172,14 @@
       <c r="N37" s="9">
         <v>59</v>
       </c>
-      <c r="O37" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O37" s="15">
+        <v>1</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>251801037</v>
       </c>
@@ -3474,11 +4222,14 @@
       <c r="N38" s="9">
         <v>43</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O38" s="11">
+        <v>4</v>
+      </c>
+      <c r="P38" s="17" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>251801038</v>
       </c>
@@ -3521,11 +4272,14 @@
       <c r="N39" s="9">
         <v>57</v>
       </c>
-      <c r="O39" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O39" s="15">
+        <v>0</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>251801039</v>
       </c>
@@ -3568,11 +4322,14 @@
       <c r="N40" s="9">
         <v>40</v>
       </c>
-      <c r="O40" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O40" s="11">
+        <v>1</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>251801040</v>
       </c>
@@ -3615,11 +4372,14 @@
       <c r="N41" s="9">
         <v>58</v>
       </c>
-      <c r="O41" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O41" s="11">
+        <v>0</v>
+      </c>
+      <c r="P41" s="12" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>251801041</v>
       </c>
@@ -3642,7 +4402,7 @@
         <v>86.84</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I42" s="7">
         <v>91.07</v>
@@ -3662,11 +4422,14 @@
       <c r="N42" s="9">
         <v>41</v>
       </c>
-      <c r="O42" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O42" s="11">
+        <v>2</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>251801042</v>
       </c>
@@ -3701,7 +4464,7 @@
         <v>62.69</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M43" s="7">
         <v>77.78</v>
@@ -3709,11 +4472,14 @@
       <c r="N43" s="9">
         <v>54</v>
       </c>
-      <c r="O43" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O43" s="11">
+        <v>6</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>251801043</v>
       </c>
@@ -3756,11 +4522,14 @@
       <c r="N44" s="9">
         <v>57</v>
       </c>
-      <c r="O44" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O44" s="15">
+        <v>1</v>
+      </c>
+      <c r="P44" s="16" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>251801044</v>
       </c>
@@ -3803,11 +4572,14 @@
       <c r="N45" s="9">
         <v>42</v>
       </c>
-      <c r="O45" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O45" s="11">
+        <v>1</v>
+      </c>
+      <c r="P45" s="12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>251801045</v>
       </c>
@@ -3850,11 +4622,14 @@
       <c r="N46" s="9">
         <v>71</v>
       </c>
-      <c r="O46" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O46" s="11">
+        <v>0</v>
+      </c>
+      <c r="P46" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>251801046</v>
       </c>
@@ -3897,11 +4672,14 @@
       <c r="N47" s="9">
         <v>56</v>
       </c>
-      <c r="O47" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O47" s="11">
+        <v>3</v>
+      </c>
+      <c r="P47" s="12" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>251801047</v>
       </c>
@@ -3944,11 +4722,14 @@
       <c r="N48" s="9">
         <v>46</v>
       </c>
-      <c r="O48" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O48" s="11">
+        <v>2</v>
+      </c>
+      <c r="P48" s="12" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>251801048</v>
       </c>
@@ -3991,11 +4772,14 @@
       <c r="N49" s="9">
         <v>72</v>
       </c>
-      <c r="O49" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O49" s="11">
+        <v>0</v>
+      </c>
+      <c r="P49" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>251801049</v>
       </c>
@@ -4038,11 +4822,14 @@
       <c r="N50" s="9">
         <v>39</v>
       </c>
-      <c r="O50" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O50" s="11">
+        <v>1</v>
+      </c>
+      <c r="P50" s="12" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>251801050</v>
       </c>
@@ -4085,11 +4872,14 @@
       <c r="N51" s="9">
         <v>38</v>
       </c>
-      <c r="O51" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O51" s="11">
+        <v>3</v>
+      </c>
+      <c r="P51" s="12" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>251801051</v>
       </c>
@@ -4132,11 +4922,14 @@
       <c r="N52" s="9">
         <v>66</v>
       </c>
-      <c r="O52" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O52" s="11">
+        <v>0</v>
+      </c>
+      <c r="P52" s="12" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>251801052</v>
       </c>
@@ -4179,11 +4972,14 @@
       <c r="N53" s="9">
         <v>72</v>
       </c>
-      <c r="O53" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O53" s="11">
+        <v>4</v>
+      </c>
+      <c r="P53" s="12" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>251801053</v>
       </c>
@@ -4226,11 +5022,14 @@
       <c r="N54" s="9">
         <v>53</v>
       </c>
-      <c r="O54" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O54" s="11">
+        <v>0</v>
+      </c>
+      <c r="P54" s="12" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>251801054</v>
       </c>
@@ -4253,7 +5052,7 @@
         <v>89.29</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I55" s="7">
         <v>80.56</v>
@@ -4273,11 +5072,14 @@
       <c r="N55" s="9">
         <v>49</v>
       </c>
-      <c r="O55" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O55" s="11">
+        <v>0</v>
+      </c>
+      <c r="P55" s="12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>251801055</v>
       </c>
@@ -4320,11 +5122,14 @@
       <c r="N56" s="9">
         <v>20</v>
       </c>
-      <c r="O56" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O56" s="11">
+        <v>7</v>
+      </c>
+      <c r="P56" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>251801056</v>
       </c>
@@ -4367,11 +5172,14 @@
       <c r="N57" s="9">
         <v>69</v>
       </c>
-      <c r="O57" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O57" s="11">
+        <v>0</v>
+      </c>
+      <c r="P57" s="12" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>251801057</v>
       </c>
@@ -4414,11 +5222,14 @@
       <c r="N58" s="9">
         <v>67</v>
       </c>
-      <c r="O58" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O58" s="11">
+        <v>0</v>
+      </c>
+      <c r="P58" s="12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>251801058</v>
       </c>
@@ -4461,11 +5272,14 @@
       <c r="N59" s="9">
         <v>70</v>
       </c>
-      <c r="O59" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O59" s="11">
+        <v>1</v>
+      </c>
+      <c r="P59" s="12" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>251801059</v>
       </c>
@@ -4508,11 +5322,14 @@
       <c r="N60" s="9">
         <v>38</v>
       </c>
-      <c r="O60" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O60" s="11">
+        <v>3</v>
+      </c>
+      <c r="P60" s="12" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>251801060</v>
       </c>
@@ -4555,11 +5372,14 @@
       <c r="N61" s="9">
         <v>52</v>
       </c>
-      <c r="O61" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O61" s="11">
+        <v>0</v>
+      </c>
+      <c r="P61" s="12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>251801061</v>
       </c>
@@ -4602,11 +5422,14 @@
       <c r="N62" s="9">
         <v>70</v>
       </c>
-      <c r="O62" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O62" s="11">
+        <v>0</v>
+      </c>
+      <c r="P62" s="12" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>251801062</v>
       </c>
@@ -4649,11 +5472,14 @@
       <c r="N63" s="9">
         <v>58</v>
       </c>
-      <c r="O63" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O63" s="11">
+        <v>1</v>
+      </c>
+      <c r="P63" s="12" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>251801063</v>
       </c>
@@ -4696,11 +5522,14 @@
       <c r="N64" s="9">
         <v>67</v>
       </c>
-      <c r="O64" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O64" s="11">
+        <v>0</v>
+      </c>
+      <c r="P64" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>251801064</v>
       </c>
@@ -4743,11 +5572,14 @@
       <c r="N65" s="9">
         <v>39</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O65" s="13">
+        <v>0</v>
+      </c>
+      <c r="P65" s="14" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>251801065</v>
       </c>
@@ -4790,11 +5622,14 @@
       <c r="N66" s="9">
         <v>59</v>
       </c>
-      <c r="O66" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O66" s="11">
+        <v>5</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>251801066</v>
       </c>
@@ -4837,11 +5672,14 @@
       <c r="N67" s="9">
         <v>64</v>
       </c>
-      <c r="O67" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O67" s="11">
+        <v>1</v>
+      </c>
+      <c r="P67" s="12" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>251801067</v>
       </c>
@@ -4884,11 +5722,14 @@
       <c r="N68" s="9">
         <v>73</v>
       </c>
-      <c r="O68" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O68" s="11">
+        <v>0</v>
+      </c>
+      <c r="P68" s="12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>251801068</v>
       </c>
@@ -4931,11 +5772,14 @@
       <c r="N69" s="9">
         <v>46</v>
       </c>
-      <c r="O69" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O69" s="11">
+        <v>0</v>
+      </c>
+      <c r="P69" s="12" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>251801069</v>
       </c>
@@ -4978,11 +5822,14 @@
       <c r="N70" s="9">
         <v>52</v>
       </c>
-      <c r="O70" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O70" s="13">
+        <v>3</v>
+      </c>
+      <c r="P70" s="14" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>251801070</v>
       </c>
@@ -5025,11 +5872,14 @@
       <c r="N71" s="9">
         <v>54</v>
       </c>
-      <c r="O71" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O71" s="11">
+        <v>3</v>
+      </c>
+      <c r="P71" s="12" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>251801071</v>
       </c>
@@ -5072,11 +5922,14 @@
       <c r="N72" s="9">
         <v>65</v>
       </c>
-      <c r="O72" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O72" s="11">
+        <v>0</v>
+      </c>
+      <c r="P72" s="12" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>251801072</v>
       </c>
@@ -5119,11 +5972,14 @@
       <c r="N73" s="9">
         <v>56</v>
       </c>
-      <c r="O73" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O73" s="11">
+        <v>3</v>
+      </c>
+      <c r="P73" s="12" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>251801073</v>
       </c>
@@ -5166,11 +6022,14 @@
       <c r="N74" s="9">
         <v>43</v>
       </c>
-      <c r="O74" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O74" s="11">
+        <v>8</v>
+      </c>
+      <c r="P74" s="12" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>251801074</v>
       </c>
@@ -5213,11 +6072,14 @@
       <c r="N75" s="9">
         <v>49</v>
       </c>
-      <c r="O75" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O75" s="11">
+        <v>4</v>
+      </c>
+      <c r="P75" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>251801075</v>
       </c>
@@ -5260,11 +6122,14 @@
       <c r="N76" s="9">
         <v>70</v>
       </c>
-      <c r="O76" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O76" s="11">
+        <v>0</v>
+      </c>
+      <c r="P76" s="12" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>251801076</v>
       </c>
@@ -5307,11 +6172,14 @@
       <c r="N77" s="9">
         <v>42</v>
       </c>
-      <c r="O77" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O77" s="11">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>251801078</v>
       </c>
@@ -5354,11 +6222,14 @@
       <c r="N78" s="9">
         <v>68</v>
       </c>
-      <c r="O78" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O78" s="11">
+        <v>0</v>
+      </c>
+      <c r="P78" s="12" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>251801079</v>
       </c>
@@ -5401,11 +6272,14 @@
       <c r="N79" s="9">
         <v>68</v>
       </c>
-      <c r="O79" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O79" s="11">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>251801080</v>
       </c>
@@ -5448,11 +6322,14 @@
       <c r="N80" s="9">
         <v>33</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O80" s="11">
+        <v>7</v>
+      </c>
+      <c r="P80" s="12" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>251801081</v>
       </c>
@@ -5495,11 +6372,14 @@
       <c r="N81" s="9">
         <v>51</v>
       </c>
-      <c r="O81" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O81" s="11">
+        <v>3</v>
+      </c>
+      <c r="P81" s="12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>251801082</v>
       </c>
@@ -5542,11 +6422,14 @@
       <c r="N82" s="9">
         <v>46</v>
       </c>
-      <c r="O82" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O82" s="11">
+        <v>1</v>
+      </c>
+      <c r="P82" s="12" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>251801083</v>
       </c>
@@ -5589,11 +6472,14 @@
       <c r="N83" s="9">
         <v>72</v>
       </c>
-      <c r="O83" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O83" s="11">
+        <v>0</v>
+      </c>
+      <c r="P83" s="12" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>251801084</v>
       </c>
@@ -5636,11 +6522,14 @@
       <c r="N84" s="9">
         <v>45</v>
       </c>
-      <c r="O84" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O84" s="11">
+        <v>0</v>
+      </c>
+      <c r="P84" s="12" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>251801085</v>
       </c>
@@ -5663,7 +6552,7 @@
         <v>96.43</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I85" s="7">
         <v>97.22</v>
@@ -5675,7 +6564,7 @@
         <v>100</v>
       </c>
       <c r="L85" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M85" s="7">
         <v>100</v>
@@ -5683,11 +6572,14 @@
       <c r="N85" s="9">
         <v>75</v>
       </c>
-      <c r="O85" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O85" s="11">
+        <v>4</v>
+      </c>
+      <c r="P85" s="12" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>251801086</v>
       </c>
@@ -5710,13 +6602,13 @@
         <v>97.3</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I86" s="7">
         <v>91.43</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K86" s="7">
         <v>88.06</v>
@@ -5730,11 +6622,14 @@
       <c r="N86" s="9">
         <v>10</v>
       </c>
-      <c r="O86" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O86" s="11">
+        <v>7</v>
+      </c>
+      <c r="P86" s="12" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>251801087</v>
       </c>
@@ -5777,11 +6672,14 @@
       <c r="N87" s="9">
         <v>55</v>
       </c>
-      <c r="O87" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O87" s="11">
+        <v>0</v>
+      </c>
+      <c r="P87" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>251801088</v>
       </c>
@@ -5824,11 +6722,14 @@
       <c r="N88" s="9">
         <v>52</v>
       </c>
-      <c r="O88" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O88" s="11">
+        <v>0</v>
+      </c>
+      <c r="P88" s="12" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>251801089</v>
       </c>
@@ -5871,11 +6772,14 @@
       <c r="N89" s="9">
         <v>48</v>
       </c>
-      <c r="O89" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O89" s="11">
+        <v>2</v>
+      </c>
+      <c r="P89" s="12" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>251801090</v>
       </c>
@@ -5918,11 +6822,14 @@
       <c r="N90" s="9">
         <v>59</v>
       </c>
-      <c r="O90" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O90" s="11">
+        <v>0</v>
+      </c>
+      <c r="P90" s="12" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>251801091</v>
       </c>
@@ -5965,11 +6872,14 @@
       <c r="N91" s="9">
         <v>61</v>
       </c>
-      <c r="O91" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O91" s="11">
+        <v>0</v>
+      </c>
+      <c r="P91" s="12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>251801092</v>
       </c>
@@ -6012,11 +6922,14 @@
       <c r="N92" s="9">
         <v>38</v>
       </c>
-      <c r="O92" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O92" s="11">
+        <v>3</v>
+      </c>
+      <c r="P92" s="12" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>251801093</v>
       </c>
@@ -6059,11 +6972,14 @@
       <c r="N93" s="9">
         <v>51</v>
       </c>
-      <c r="O93" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O93" s="13">
+        <v>0</v>
+      </c>
+      <c r="P93" s="14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>251801094</v>
       </c>
@@ -6106,11 +7022,14 @@
       <c r="N94" s="9">
         <v>39</v>
       </c>
-      <c r="O94" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O94" s="13">
+        <v>2</v>
+      </c>
+      <c r="P94" s="14" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>251801095</v>
       </c>
@@ -6139,7 +7058,7 @@
         <v>84.38</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K95" s="7">
         <v>72.31</v>
@@ -6153,11 +7072,14 @@
       <c r="N95" s="9">
         <v>48</v>
       </c>
-      <c r="O95" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O95" s="11">
+        <v>4</v>
+      </c>
+      <c r="P95" s="12" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>251801096</v>
       </c>
@@ -6200,11 +7122,14 @@
       <c r="N96" s="9">
         <v>38</v>
       </c>
-      <c r="O96" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O96" s="11">
+        <v>1</v>
+      </c>
+      <c r="P96" s="12" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>251801097</v>
       </c>
@@ -6247,11 +7172,14 @@
       <c r="N97" s="9">
         <v>66</v>
       </c>
-      <c r="O97" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O97" s="11">
+        <v>0</v>
+      </c>
+      <c r="P97" s="12" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>251801098</v>
       </c>
@@ -6294,11 +7222,14 @@
       <c r="N98" s="9">
         <v>62</v>
       </c>
-      <c r="O98" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O98" s="11">
+        <v>0</v>
+      </c>
+      <c r="P98" s="12" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>251801099</v>
       </c>
@@ -6341,11 +7272,14 @@
       <c r="N99" s="9">
         <v>59</v>
       </c>
-      <c r="O99" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O99" s="15">
+        <v>0</v>
+      </c>
+      <c r="P99" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>251801100</v>
       </c>
@@ -6388,11 +7322,14 @@
       <c r="N100" s="9">
         <v>59</v>
       </c>
-      <c r="O100" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O100" s="13">
+        <v>0</v>
+      </c>
+      <c r="P100" s="14" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>251801101</v>
       </c>
@@ -6435,11 +7372,14 @@
       <c r="N101" s="9">
         <v>51</v>
       </c>
-      <c r="O101" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O101" s="11">
+        <v>0</v>
+      </c>
+      <c r="P101" s="12" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>251801102</v>
       </c>
@@ -6482,11 +7422,14 @@
       <c r="N102" s="9">
         <v>61</v>
       </c>
-      <c r="O102" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O102" s="11">
+        <v>0</v>
+      </c>
+      <c r="P102" s="12" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>251801103</v>
       </c>
@@ -6529,11 +7472,14 @@
       <c r="N103" s="9">
         <v>59</v>
       </c>
-      <c r="O103" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O103" s="11">
+        <v>0</v>
+      </c>
+      <c r="P103" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>251801104</v>
       </c>
@@ -6576,11 +7522,14 @@
       <c r="N104" s="9">
         <v>60</v>
       </c>
-      <c r="O104" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O104" s="11">
+        <v>5</v>
+      </c>
+      <c r="P104" s="12" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>251801105</v>
       </c>
@@ -6623,11 +7572,14 @@
       <c r="N105" s="9">
         <v>39</v>
       </c>
-      <c r="O105" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O105" s="11">
+        <v>0</v>
+      </c>
+      <c r="P105" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>251801106</v>
       </c>
@@ -6670,11 +7622,14 @@
       <c r="N106" s="9">
         <v>62</v>
       </c>
-      <c r="O106" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O106" s="11">
+        <v>1</v>
+      </c>
+      <c r="P106" s="12" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>251801107</v>
       </c>
@@ -6717,11 +7672,14 @@
       <c r="N107" s="9">
         <v>38</v>
       </c>
-      <c r="O107" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O107" s="11">
+        <v>8</v>
+      </c>
+      <c r="P107" s="14" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>251801108</v>
       </c>
@@ -6764,11 +7722,14 @@
       <c r="N108" s="9">
         <v>69</v>
       </c>
-      <c r="O108" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O108" s="11">
+        <v>0</v>
+      </c>
+      <c r="P108" s="12" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>251801109</v>
       </c>
@@ -6811,11 +7772,14 @@
       <c r="N109" s="9">
         <v>43</v>
       </c>
-      <c r="O109" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O109" s="11">
+        <v>1</v>
+      </c>
+      <c r="P109" s="12" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>251801110</v>
       </c>
@@ -6858,11 +7822,14 @@
       <c r="N110" s="9">
         <v>40</v>
       </c>
-      <c r="O110" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O110" s="11">
+        <v>0</v>
+      </c>
+      <c r="P110" s="12" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>251801111</v>
       </c>
@@ -6905,11 +7872,14 @@
       <c r="N111" s="9">
         <v>63</v>
       </c>
-      <c r="O111" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O111" s="11">
+        <v>0</v>
+      </c>
+      <c r="P111" s="12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>251801112</v>
       </c>
@@ -6952,11 +7922,14 @@
       <c r="N112" s="9">
         <v>68</v>
       </c>
-      <c r="O112" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O112" s="11">
+        <v>0</v>
+      </c>
+      <c r="P112" s="12" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>251801113</v>
       </c>
@@ -6999,11 +7972,14 @@
       <c r="N113" s="9">
         <v>57</v>
       </c>
-      <c r="O113" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O113" s="11">
+        <v>0</v>
+      </c>
+      <c r="P113" s="12" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>251801114</v>
       </c>
@@ -7046,11 +8022,14 @@
       <c r="N114" s="9">
         <v>38</v>
       </c>
-      <c r="O114" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O114" s="11">
+        <v>0</v>
+      </c>
+      <c r="P114" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>251801115</v>
       </c>
@@ -7093,11 +8072,14 @@
       <c r="N115" s="9">
         <v>68</v>
       </c>
-      <c r="O115" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O115" s="11">
+        <v>0</v>
+      </c>
+      <c r="P115" s="12" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>251801116</v>
       </c>
@@ -7140,11 +8122,14 @@
       <c r="N116" s="9">
         <v>60</v>
       </c>
-      <c r="O116" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O116" s="11">
+        <v>0</v>
+      </c>
+      <c r="P116" s="12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>251801117</v>
       </c>
@@ -7187,11 +8172,14 @@
       <c r="N117" s="9">
         <v>69</v>
       </c>
-      <c r="O117" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O117" s="11">
+        <v>0</v>
+      </c>
+      <c r="P117" s="12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>251801118</v>
       </c>
@@ -7234,11 +8222,14 @@
       <c r="N118" s="9">
         <v>67</v>
       </c>
-      <c r="O118" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O118" s="11">
+        <v>0</v>
+      </c>
+      <c r="P118" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>251801119</v>
       </c>
@@ -7281,11 +8272,14 @@
       <c r="N119" s="9">
         <v>59</v>
       </c>
-      <c r="O119" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O119" s="11">
+        <v>0</v>
+      </c>
+      <c r="P119" s="12" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>251801120</v>
       </c>
@@ -7328,11 +8322,14 @@
       <c r="N120" s="9">
         <v>68</v>
       </c>
-      <c r="O120" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O120" s="13">
+        <v>0</v>
+      </c>
+      <c r="P120" s="14" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>251801122</v>
       </c>
@@ -7375,11 +8372,14 @@
       <c r="N121" s="9">
         <v>48</v>
       </c>
-      <c r="O121" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O121" s="11">
+        <v>0</v>
+      </c>
+      <c r="P121" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>251801123</v>
       </c>
@@ -7422,11 +8422,14 @@
       <c r="N122" s="9">
         <v>49</v>
       </c>
-      <c r="O122" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O122" s="11">
+        <v>4</v>
+      </c>
+      <c r="P122" s="12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>251801124</v>
       </c>
@@ -7469,11 +8472,14 @@
       <c r="N123" s="9">
         <v>60</v>
       </c>
-      <c r="O123" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O123" s="11">
+        <v>0</v>
+      </c>
+      <c r="P123" s="12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>251801125</v>
       </c>
@@ -7516,11 +8522,14 @@
       <c r="N124" s="9">
         <v>42</v>
       </c>
-      <c r="O124" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O124" s="11">
+        <v>2</v>
+      </c>
+      <c r="P124" s="12" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>251801126</v>
       </c>
@@ -7563,11 +8572,14 @@
       <c r="N125" s="9">
         <v>69</v>
       </c>
-      <c r="O125" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O125" s="11">
+        <v>0</v>
+      </c>
+      <c r="P125" s="12" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>251801127</v>
       </c>
@@ -7610,11 +8622,14 @@
       <c r="N126" s="9">
         <v>56</v>
       </c>
-      <c r="O126" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O126" s="11">
+        <v>0</v>
+      </c>
+      <c r="P126" s="12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>251801128</v>
       </c>
@@ -7649,7 +8664,7 @@
         <v>73.849999999999994</v>
       </c>
       <c r="L127" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M127" s="7">
         <v>100</v>
@@ -7657,11 +8672,14 @@
       <c r="N127" s="9">
         <v>38</v>
       </c>
-      <c r="O127" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O127" s="11">
+        <v>1</v>
+      </c>
+      <c r="P127" s="12" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>251801129</v>
       </c>
@@ -7704,11 +8722,14 @@
       <c r="N128" s="9">
         <v>61</v>
       </c>
-      <c r="O128" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O128" s="11">
+        <v>0</v>
+      </c>
+      <c r="P128" s="12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>251801130</v>
       </c>
@@ -7751,11 +8772,14 @@
       <c r="N129" s="9">
         <v>50</v>
       </c>
-      <c r="O129" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O129" s="11">
+        <v>0</v>
+      </c>
+      <c r="P129" s="12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>251801131</v>
       </c>
@@ -7778,19 +8802,19 @@
         <v>100</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I130" s="7">
         <v>97.22</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K130" s="7">
         <v>92.86</v>
       </c>
       <c r="L130" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M130" s="7">
         <v>100</v>
@@ -7798,11 +8822,14 @@
       <c r="N130" s="9">
         <v>67</v>
       </c>
-      <c r="O130" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O130" s="11">
+        <v>1</v>
+      </c>
+      <c r="P130" s="12" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>251801132</v>
       </c>
@@ -7845,11 +8872,14 @@
       <c r="N131" s="9">
         <v>60</v>
       </c>
-      <c r="O131" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O131" s="15">
+        <v>0</v>
+      </c>
+      <c r="P131" s="16" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>251801133</v>
       </c>
@@ -7892,11 +8922,14 @@
       <c r="N132" s="9">
         <v>61</v>
       </c>
-      <c r="O132" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O132" s="13">
+        <v>0</v>
+      </c>
+      <c r="P132" s="14" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>251801134</v>
       </c>
@@ -7939,11 +8972,14 @@
       <c r="N133" s="9">
         <v>68</v>
       </c>
-      <c r="O133" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O133" s="11">
+        <v>0</v>
+      </c>
+      <c r="P133" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>251801135</v>
       </c>
@@ -7986,11 +9022,14 @@
       <c r="N134" s="9">
         <v>48</v>
       </c>
-      <c r="O134" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O134" s="11">
+        <v>0</v>
+      </c>
+      <c r="P134" s="12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>251801136</v>
       </c>
@@ -8033,11 +9072,14 @@
       <c r="N135" s="9">
         <v>65</v>
       </c>
-      <c r="O135" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O135" s="11">
+        <v>0</v>
+      </c>
+      <c r="P135" s="12" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>251801137</v>
       </c>
@@ -8080,11 +9122,14 @@
       <c r="N136" s="9">
         <v>43</v>
       </c>
-      <c r="O136" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O136" s="11">
+        <v>2</v>
+      </c>
+      <c r="P136" s="12" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>251801138</v>
       </c>
@@ -8127,11 +9172,14 @@
       <c r="N137" s="9">
         <v>60</v>
       </c>
-      <c r="O137" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O137" s="11">
+        <v>1</v>
+      </c>
+      <c r="P137" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>251801139</v>
       </c>
@@ -8174,11 +9222,14 @@
       <c r="N138" s="9">
         <v>28</v>
       </c>
-      <c r="O138" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O138" s="11">
+        <v>3</v>
+      </c>
+      <c r="P138" s="12" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>251801140</v>
       </c>
@@ -8221,11 +9272,14 @@
       <c r="N139" s="9">
         <v>45</v>
       </c>
-      <c r="O139" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O139" s="11">
+        <v>2</v>
+      </c>
+      <c r="P139" s="12" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>251801141</v>
       </c>
@@ -8268,11 +9322,14 @@
       <c r="N140" s="9">
         <v>67</v>
       </c>
-      <c r="O140" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O140" s="11">
+        <v>0</v>
+      </c>
+      <c r="P140" s="12" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>251801142</v>
       </c>
@@ -8315,11 +9372,14 @@
       <c r="N141" s="9">
         <v>52</v>
       </c>
-      <c r="O141" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O141" s="13">
+        <v>0</v>
+      </c>
+      <c r="P141" s="14" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>251801143</v>
       </c>
@@ -8362,11 +9422,14 @@
       <c r="N142" s="9">
         <v>68</v>
       </c>
-      <c r="O142" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O142" s="11">
+        <v>1</v>
+      </c>
+      <c r="P142" s="14" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>251801144</v>
       </c>
@@ -8409,11 +9472,14 @@
       <c r="N143" s="9">
         <v>54</v>
       </c>
-      <c r="O143" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O143" s="11">
+        <v>0</v>
+      </c>
+      <c r="P143" s="12" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>251801145</v>
       </c>
@@ -8456,11 +9522,14 @@
       <c r="N144" s="9">
         <v>64</v>
       </c>
-      <c r="O144" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O144" s="11">
+        <v>1</v>
+      </c>
+      <c r="P144" s="12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>251801146</v>
       </c>
@@ -8503,11 +9572,14 @@
       <c r="N145" s="9">
         <v>56</v>
       </c>
-      <c r="O145" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O145" s="11">
+        <v>0</v>
+      </c>
+      <c r="P145" s="12" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>251801147</v>
       </c>
@@ -8550,11 +9622,14 @@
       <c r="N146" s="9">
         <v>57</v>
       </c>
-      <c r="O146" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O146" s="11">
+        <v>0</v>
+      </c>
+      <c r="P146" s="12" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>251801148</v>
       </c>
@@ -8597,11 +9672,14 @@
       <c r="N147" s="9">
         <v>62</v>
       </c>
-      <c r="O147" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O147" s="11">
+        <v>1</v>
+      </c>
+      <c r="P147" s="12" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>251801149</v>
       </c>
@@ -8644,11 +9722,14 @@
       <c r="N148" s="9">
         <v>70</v>
       </c>
-      <c r="O148" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O148" s="11">
+        <v>0</v>
+      </c>
+      <c r="P148" s="12" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>251801150</v>
       </c>
@@ -8691,11 +9772,14 @@
       <c r="N149" s="9">
         <v>6</v>
       </c>
-      <c r="O149" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O149" s="11">
+        <v>4</v>
+      </c>
+      <c r="P149" s="12" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>251801151</v>
       </c>
@@ -8738,11 +9822,14 @@
       <c r="N150" s="9">
         <v>43</v>
       </c>
-      <c r="O150" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O150" s="11">
+        <v>0</v>
+      </c>
+      <c r="P150" s="12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>251801152</v>
       </c>
@@ -8785,11 +9872,14 @@
       <c r="N151" s="9">
         <v>63</v>
       </c>
-      <c r="O151" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O151" s="11">
+        <v>1</v>
+      </c>
+      <c r="P151" s="12" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>251801153</v>
       </c>
@@ -8832,11 +9922,14 @@
       <c r="N152" s="9">
         <v>43</v>
       </c>
-      <c r="O152" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O152" s="11">
+        <v>6</v>
+      </c>
+      <c r="P152" s="12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>251801154</v>
       </c>
@@ -8879,11 +9972,14 @@
       <c r="N153" s="9">
         <v>57</v>
       </c>
-      <c r="O153" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O153" s="11">
+        <v>2</v>
+      </c>
+      <c r="P153" s="12" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>251801155</v>
       </c>
@@ -8926,11 +10022,14 @@
       <c r="N154" s="9">
         <v>53</v>
       </c>
-      <c r="O154" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O154" s="11">
+        <v>1</v>
+      </c>
+      <c r="P154" s="12" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>251801156</v>
       </c>
@@ -8973,11 +10072,14 @@
       <c r="N155" s="9">
         <v>72</v>
       </c>
-      <c r="O155" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O155" s="11">
+        <v>0</v>
+      </c>
+      <c r="P155" s="12" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>251801157</v>
       </c>
@@ -9020,11 +10122,14 @@
       <c r="N156" s="9">
         <v>39</v>
       </c>
-      <c r="O156" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O156" s="11">
+        <v>0</v>
+      </c>
+      <c r="P156" s="12" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>251801158</v>
       </c>
@@ -9067,11 +10172,14 @@
       <c r="N157" s="9">
         <v>38</v>
       </c>
-      <c r="O157" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O157" s="13">
+        <v>0</v>
+      </c>
+      <c r="P157" s="14" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>251801159</v>
       </c>
@@ -9114,11 +10222,14 @@
       <c r="N158" s="9">
         <v>39</v>
       </c>
-      <c r="O158" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O158" s="11">
+        <v>5</v>
+      </c>
+      <c r="P158" s="12" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>251801160</v>
       </c>
@@ -9161,11 +10272,14 @@
       <c r="N159" s="9">
         <v>46</v>
       </c>
-      <c r="O159" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O159" s="11">
+        <v>1</v>
+      </c>
+      <c r="P159" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>251801161</v>
       </c>
@@ -9208,11 +10322,14 @@
       <c r="N160" s="9">
         <v>46</v>
       </c>
-      <c r="O160" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O160" s="13">
+        <v>0</v>
+      </c>
+      <c r="P160" s="14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>251801162</v>
       </c>
@@ -9255,11 +10372,14 @@
       <c r="N161" s="9">
         <v>60</v>
       </c>
-      <c r="O161" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O161" s="11">
+        <v>2</v>
+      </c>
+      <c r="P161" s="12" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>251801163</v>
       </c>
@@ -9302,11 +10422,14 @@
       <c r="N162" s="9">
         <v>57</v>
       </c>
-      <c r="O162" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O162" s="11">
+        <v>2</v>
+      </c>
+      <c r="P162" s="12" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>251801164</v>
       </c>
@@ -9349,11 +10472,14 @@
       <c r="N163" s="9">
         <v>61</v>
       </c>
-      <c r="O163" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O163" s="11">
+        <v>0</v>
+      </c>
+      <c r="P163" s="12" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>251801165</v>
       </c>
@@ -9396,11 +10522,14 @@
       <c r="N164" s="9">
         <v>59</v>
       </c>
-      <c r="O164" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O164" s="11">
+        <v>0</v>
+      </c>
+      <c r="P164" s="12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>251801166</v>
       </c>
@@ -9443,11 +10572,14 @@
       <c r="N165" s="9">
         <v>71</v>
       </c>
-      <c r="O165" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O165" s="11">
+        <v>0</v>
+      </c>
+      <c r="P165" s="12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>251801167</v>
       </c>
@@ -9490,11 +10622,14 @@
       <c r="N166" s="9">
         <v>66</v>
       </c>
-      <c r="O166" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O166" s="11">
+        <v>0</v>
+      </c>
+      <c r="P166" s="12" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>251801168</v>
       </c>
@@ -9537,11 +10672,14 @@
       <c r="N167" s="9">
         <v>61</v>
       </c>
-      <c r="O167" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O167" s="11">
+        <v>0</v>
+      </c>
+      <c r="P167" s="12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>251801169</v>
       </c>
@@ -9584,11 +10722,14 @@
       <c r="N168" s="9">
         <v>49</v>
       </c>
-      <c r="O168" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O168" s="11">
+        <v>1</v>
+      </c>
+      <c r="P168" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>251801170</v>
       </c>
@@ -9631,11 +10772,14 @@
       <c r="N169" s="9">
         <v>58</v>
       </c>
-      <c r="O169" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O169" s="11">
+        <v>2</v>
+      </c>
+      <c r="P169" s="12" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>251801171</v>
       </c>
@@ -9678,11 +10822,14 @@
       <c r="N170" s="9">
         <v>72</v>
       </c>
-      <c r="O170" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O170" s="11">
+        <v>1</v>
+      </c>
+      <c r="P170" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>251801172</v>
       </c>
@@ -9725,11 +10872,14 @@
       <c r="N171" s="9">
         <v>32</v>
       </c>
-      <c r="O171" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O171" s="11">
+        <v>0</v>
+      </c>
+      <c r="P171" s="12" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>251801173</v>
       </c>
@@ -9772,11 +10922,14 @@
       <c r="N172" s="9">
         <v>53</v>
       </c>
-      <c r="O172" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O172" s="11">
+        <v>0</v>
+      </c>
+      <c r="P172" s="12" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>251801174</v>
       </c>
@@ -9819,11 +10972,14 @@
       <c r="N173" s="9">
         <v>38</v>
       </c>
-      <c r="O173" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O173" s="11">
+        <v>0</v>
+      </c>
+      <c r="P173" s="12" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>251801175</v>
       </c>
@@ -9866,11 +11022,14 @@
       <c r="N174" s="9">
         <v>62</v>
       </c>
-      <c r="O174" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O174" s="11">
+        <v>4</v>
+      </c>
+      <c r="P174" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>251801176</v>
       </c>
@@ -9913,11 +11072,14 @@
       <c r="N175" s="9">
         <v>50</v>
       </c>
-      <c r="O175" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O175" s="11">
+        <v>7</v>
+      </c>
+      <c r="P175" s="12" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>251801177</v>
       </c>
@@ -9960,11 +11122,14 @@
       <c r="N176" s="9">
         <v>64</v>
       </c>
-      <c r="O176" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O176" s="15">
+        <v>0</v>
+      </c>
+      <c r="P176" s="16" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>251801178</v>
       </c>
@@ -10007,11 +11172,14 @@
       <c r="N177" s="9">
         <v>67</v>
       </c>
-      <c r="O177" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O177" s="11">
+        <v>0</v>
+      </c>
+      <c r="P177" s="12" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>251801179</v>
       </c>
@@ -10054,11 +11222,14 @@
       <c r="N178" s="9">
         <v>68</v>
       </c>
-      <c r="O178" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O178" s="11">
+        <v>0</v>
+      </c>
+      <c r="P178" s="12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>251801180</v>
       </c>
@@ -10101,11 +11272,14 @@
       <c r="N179" s="9">
         <v>70</v>
       </c>
-      <c r="O179" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O179" s="13">
+        <v>2</v>
+      </c>
+      <c r="P179" s="14" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>251801181</v>
       </c>
@@ -10148,11 +11322,14 @@
       <c r="N180" s="9">
         <v>71</v>
       </c>
-      <c r="O180" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O180" s="13">
+        <v>0</v>
+      </c>
+      <c r="P180" s="14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>251801182</v>
       </c>
@@ -10195,11 +11372,14 @@
       <c r="N181" s="9">
         <v>72</v>
       </c>
-      <c r="O181" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O181" s="13">
+        <v>0</v>
+      </c>
+      <c r="P181" s="14" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>251801183</v>
       </c>
@@ -10242,11 +11422,14 @@
       <c r="N182" s="9">
         <v>66</v>
       </c>
-      <c r="O182" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O182" s="11">
+        <v>0</v>
+      </c>
+      <c r="P182" s="12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>251801184</v>
       </c>
@@ -10289,11 +11472,14 @@
       <c r="N183" s="9">
         <v>64</v>
       </c>
-      <c r="O183" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O183" s="11">
+        <v>0</v>
+      </c>
+      <c r="P183" s="12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>251801185</v>
       </c>
@@ -10336,11 +11522,14 @@
       <c r="N184" s="9">
         <v>58</v>
       </c>
-      <c r="O184" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O184" s="13">
+        <v>0</v>
+      </c>
+      <c r="P184" s="14" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>251801186</v>
       </c>
@@ -10369,7 +11558,7 @@
         <v>91.07</v>
       </c>
       <c r="J185" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K185" s="8">
         <v>86.15</v>
@@ -10383,11 +11572,14 @@
       <c r="N185" s="9">
         <v>56</v>
       </c>
-      <c r="O185" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O185" s="18">
+        <v>1</v>
+      </c>
+      <c r="P185" s="17" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>251801187</v>
       </c>
@@ -10430,11 +11622,14 @@
       <c r="N186" s="9">
         <v>58</v>
       </c>
-      <c r="O186" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O186" s="15">
+        <v>0</v>
+      </c>
+      <c r="P186" s="16" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>251801188</v>
       </c>
@@ -10477,11 +11672,14 @@
       <c r="N187" s="9">
         <v>40</v>
       </c>
-      <c r="O187" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O187" s="13">
+        <v>0</v>
+      </c>
+      <c r="P187" s="14" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>251801189</v>
       </c>
@@ -10524,11 +11722,14 @@
       <c r="N188" s="9">
         <v>64</v>
       </c>
-      <c r="O188" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O188" s="11">
+        <v>1</v>
+      </c>
+      <c r="P188" s="12" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>251801190</v>
       </c>
@@ -10571,11 +11772,14 @@
       <c r="N189" s="9">
         <v>38</v>
       </c>
-      <c r="O189" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O189" s="11">
+        <v>4</v>
+      </c>
+      <c r="P189" s="12" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>251801191</v>
       </c>
@@ -10618,11 +11822,14 @@
       <c r="N190" s="9">
         <v>56</v>
       </c>
-      <c r="O190" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O190" s="11">
+        <v>0</v>
+      </c>
+      <c r="P190" s="12" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>251801192</v>
       </c>
@@ -10665,11 +11872,14 @@
       <c r="N191" s="9">
         <v>48</v>
       </c>
-      <c r="O191" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O191" s="11">
+        <v>0</v>
+      </c>
+      <c r="P191" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>251801193</v>
       </c>
@@ -10712,11 +11922,14 @@
       <c r="N192" s="9">
         <v>47</v>
       </c>
-      <c r="O192" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O192" s="11">
+        <v>1</v>
+      </c>
+      <c r="P192" s="12" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>251801194</v>
       </c>
@@ -10759,11 +11972,14 @@
       <c r="N193" s="9">
         <v>59</v>
       </c>
-      <c r="O193" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O193" s="11">
+        <v>2</v>
+      </c>
+      <c r="P193" s="12" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>251801195</v>
       </c>
@@ -10806,11 +12022,14 @@
       <c r="N194" s="9">
         <v>38</v>
       </c>
-      <c r="O194" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O194" s="11">
+        <v>4</v>
+      </c>
+      <c r="P194" s="12" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>251801196</v>
       </c>
@@ -10853,11 +12072,14 @@
       <c r="N195" s="9">
         <v>71</v>
       </c>
-      <c r="O195" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O195" s="11">
+        <v>3</v>
+      </c>
+      <c r="P195" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>251801197</v>
       </c>
@@ -10900,11 +12122,14 @@
       <c r="N196" s="9">
         <v>63</v>
       </c>
-      <c r="O196" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O196" s="15">
+        <v>0</v>
+      </c>
+      <c r="P196" s="16" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>251801198</v>
       </c>
@@ -10947,11 +12172,14 @@
       <c r="N197" s="9">
         <v>58</v>
       </c>
-      <c r="O197" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O197" s="13">
+        <v>3</v>
+      </c>
+      <c r="P197" s="14" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>251801199</v>
       </c>
@@ -10974,13 +12202,13 @@
         <v>77.03</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I198" s="7">
         <v>91.43</v>
       </c>
       <c r="J198" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K198" s="7">
         <v>79.099999999999994</v>
@@ -10994,11 +12222,14 @@
       <c r="N198" s="9">
         <v>28</v>
       </c>
-      <c r="O198" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="199" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O198" s="11">
+        <v>12</v>
+      </c>
+      <c r="P198" s="12" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>251801200</v>
       </c>
@@ -11009,7 +12240,7 @@
         <v>80</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E199" s="8">
         <v>88.37</v>
@@ -11021,13 +12252,13 @@
         <v>80.56</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I199" s="8">
         <v>92.19</v>
       </c>
       <c r="J199" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K199" s="8">
         <v>78.459999999999994</v>
@@ -11041,11 +12272,14 @@
       <c r="N199" s="9">
         <v>17</v>
       </c>
-      <c r="O199" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="200" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O199" s="11">
+        <v>5</v>
+      </c>
+      <c r="P199" s="12" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>251801202</v>
       </c>
@@ -11088,11 +12322,14 @@
       <c r="N200" s="9">
         <v>69</v>
       </c>
-      <c r="O200" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O200" s="15">
+        <v>0</v>
+      </c>
+      <c r="P200" s="16" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>251801203</v>
       </c>
@@ -11135,11 +12372,14 @@
       <c r="N201" s="9">
         <v>57</v>
       </c>
-      <c r="O201" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="202" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O201" s="13">
+        <v>4</v>
+      </c>
+      <c r="P201" s="14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>251801204</v>
       </c>
@@ -11182,11 +12422,14 @@
       <c r="N202" s="9">
         <v>51</v>
       </c>
-      <c r="O202" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="203" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O202" s="11">
+        <v>4</v>
+      </c>
+      <c r="P202" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>251801205</v>
       </c>
@@ -11229,11 +12472,14 @@
       <c r="N203" s="9">
         <v>70</v>
       </c>
-      <c r="O203" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O203" s="11">
+        <v>0</v>
+      </c>
+      <c r="P203" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>251801206</v>
       </c>
@@ -11276,11 +12522,14 @@
       <c r="N204" s="9">
         <v>74</v>
       </c>
-      <c r="O204" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O204" s="11">
+        <v>0</v>
+      </c>
+      <c r="P204" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>251801207</v>
       </c>
@@ -11323,11 +12572,14 @@
       <c r="N205" s="9">
         <v>57</v>
       </c>
-      <c r="O205" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O205" s="11">
+        <v>0</v>
+      </c>
+      <c r="P205" s="12" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>251801208</v>
       </c>
@@ -11370,11 +12622,14 @@
       <c r="N206" s="9">
         <v>65</v>
       </c>
-      <c r="O206" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O206" s="11">
+        <v>0</v>
+      </c>
+      <c r="P206" s="12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>251801209</v>
       </c>
@@ -11417,11 +12672,14 @@
       <c r="N207" s="9">
         <v>53</v>
       </c>
-      <c r="O207" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="208" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O207" s="11">
+        <v>2</v>
+      </c>
+      <c r="P207" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>251801210</v>
       </c>
@@ -11464,11 +12722,14 @@
       <c r="N208" s="9">
         <v>49</v>
       </c>
-      <c r="O208" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="209" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O208" s="11">
+        <v>1</v>
+      </c>
+      <c r="P208" s="12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>251801211</v>
       </c>
@@ -11491,7 +12752,7 @@
         <v>81.58</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I209" s="8">
         <v>80.36</v>
@@ -11511,11 +12772,14 @@
       <c r="N209" s="9">
         <v>0</v>
       </c>
-      <c r="O209" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="210" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O209" s="11">
+        <v>4</v>
+      </c>
+      <c r="P209" s="12" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>251801212</v>
       </c>
@@ -11558,11 +12822,14 @@
       <c r="N210" s="9">
         <v>69</v>
       </c>
-      <c r="O210" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="211" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O210" s="11">
+        <v>0</v>
+      </c>
+      <c r="P210" s="12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>251801213</v>
       </c>
@@ -11605,11 +12872,14 @@
       <c r="N211" s="9">
         <v>59</v>
       </c>
-      <c r="O211" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="212" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O211" s="11">
+        <v>0</v>
+      </c>
+      <c r="P211" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>251801214</v>
       </c>
@@ -11652,11 +12922,14 @@
       <c r="N212" s="9">
         <v>51</v>
       </c>
-      <c r="O212" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="213" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O212" s="11">
+        <v>0</v>
+      </c>
+      <c r="P212" s="12" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>251801215</v>
       </c>
@@ -11699,11 +12972,14 @@
       <c r="N213" s="9">
         <v>50</v>
       </c>
-      <c r="O213" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O213" s="11">
+        <v>1</v>
+      </c>
+      <c r="P213" s="12" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>251801216</v>
       </c>
@@ -11746,11 +13022,14 @@
       <c r="N214" s="9">
         <v>55</v>
       </c>
-      <c r="O214" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="215" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O214" s="11">
+        <v>1</v>
+      </c>
+      <c r="P214" s="12" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>251801217</v>
       </c>
@@ -11793,11 +13072,14 @@
       <c r="N215" s="9">
         <v>72</v>
       </c>
-      <c r="O215" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="216" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O215" s="11">
+        <v>0</v>
+      </c>
+      <c r="P215" s="12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>251801218</v>
       </c>
@@ -11840,11 +13122,14 @@
       <c r="N216" s="9">
         <v>59</v>
       </c>
-      <c r="O216" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="217" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O216" s="11">
+        <v>0</v>
+      </c>
+      <c r="P216" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>251801219</v>
       </c>
@@ -11887,11 +13172,14 @@
       <c r="N217" s="9">
         <v>38</v>
       </c>
-      <c r="O217" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="218" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O217" s="11">
+        <v>5</v>
+      </c>
+      <c r="P217" s="12" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>251801220</v>
       </c>
@@ -11934,11 +13222,14 @@
       <c r="N218" s="9">
         <v>56</v>
       </c>
-      <c r="O218" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="219" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O218" s="11">
+        <v>0</v>
+      </c>
+      <c r="P218" s="12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>251801221</v>
       </c>
@@ -11981,11 +13272,14 @@
       <c r="N219" s="9">
         <v>54</v>
       </c>
-      <c r="O219" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O219" s="11">
+        <v>0</v>
+      </c>
+      <c r="P219" s="12" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>251801223</v>
       </c>
@@ -12028,11 +13322,14 @@
       <c r="N220" s="9">
         <v>73</v>
       </c>
-      <c r="O220" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O220" s="11">
+        <v>0</v>
+      </c>
+      <c r="P220" s="12" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>251801224</v>
       </c>
@@ -12075,11 +13372,14 @@
       <c r="N221" s="9">
         <v>73</v>
       </c>
-      <c r="O221" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="222" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O221" s="11">
+        <v>6</v>
+      </c>
+      <c r="P221" s="12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>251801225</v>
       </c>
@@ -12122,11 +13422,14 @@
       <c r="N222" s="9">
         <v>72</v>
       </c>
-      <c r="O222" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="223" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O222" s="11">
+        <v>1</v>
+      </c>
+      <c r="P222" s="12" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>251801226</v>
       </c>
@@ -12169,11 +13472,14 @@
       <c r="N223" s="9">
         <v>64</v>
       </c>
-      <c r="O223" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="224" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O223" s="11">
+        <v>0</v>
+      </c>
+      <c r="P223" s="12" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>251801227</v>
       </c>
@@ -12216,11 +13522,14 @@
       <c r="N224" s="9">
         <v>68</v>
       </c>
-      <c r="O224" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O224" s="11">
+        <v>0</v>
+      </c>
+      <c r="P224" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>251801228</v>
       </c>
@@ -12263,11 +13572,14 @@
       <c r="N225" s="9">
         <v>65</v>
       </c>
-      <c r="O225" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O225" s="11">
+        <v>0</v>
+      </c>
+      <c r="P225" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>251801229</v>
       </c>
@@ -12310,11 +13622,14 @@
       <c r="N226" s="9">
         <v>61</v>
       </c>
-      <c r="O226" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O226" s="11">
+        <v>4</v>
+      </c>
+      <c r="P226" s="12" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>251801230</v>
       </c>
@@ -12357,11 +13672,14 @@
       <c r="N227" s="9">
         <v>71</v>
       </c>
-      <c r="O227" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O227" s="11">
+        <v>3</v>
+      </c>
+      <c r="P227" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>251801231</v>
       </c>
@@ -12404,11 +13722,14 @@
       <c r="N228" s="9">
         <v>48</v>
       </c>
-      <c r="O228" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O228" s="11">
+        <v>0</v>
+      </c>
+      <c r="P228" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>251801233</v>
       </c>
@@ -12451,11 +13772,14 @@
       <c r="N229" s="9">
         <v>45</v>
       </c>
-      <c r="O229" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O229" s="11">
+        <v>0</v>
+      </c>
+      <c r="P229" s="12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>251801234</v>
       </c>
@@ -12498,11 +13822,14 @@
       <c r="N230" s="9">
         <v>56</v>
       </c>
-      <c r="O230" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O230" s="11">
+        <v>0</v>
+      </c>
+      <c r="P230" s="12" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>251801235</v>
       </c>
@@ -12537,7 +13864,7 @@
         <v>72.31</v>
       </c>
       <c r="L231" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M231" s="7">
         <v>68.42</v>
@@ -12545,11 +13872,14 @@
       <c r="N231" s="9">
         <v>64</v>
       </c>
-      <c r="O231" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O231" s="11">
+        <v>0</v>
+      </c>
+      <c r="P231" s="12" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>251801236</v>
       </c>
@@ -12592,11 +13922,14 @@
       <c r="N232" s="9">
         <v>58</v>
       </c>
-      <c r="O232" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="233" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O232" s="11">
+        <v>1</v>
+      </c>
+      <c r="P232" s="12" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>251801237</v>
       </c>
@@ -12639,11 +13972,14 @@
       <c r="N233" s="9">
         <v>70</v>
       </c>
-      <c r="O233" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O233" s="11">
+        <v>2</v>
+      </c>
+      <c r="P233" s="12" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>251801238</v>
       </c>
@@ -12672,7 +14008,7 @@
         <v>88.89</v>
       </c>
       <c r="J234" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K234" s="7">
         <v>91.04</v>
@@ -12686,11 +14022,14 @@
       <c r="N234" s="9">
         <v>47</v>
       </c>
-      <c r="O234" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="235" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O234" s="11">
+        <v>0</v>
+      </c>
+      <c r="P234" s="12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>251801239</v>
       </c>
@@ -12733,11 +14072,14 @@
       <c r="N235" s="9">
         <v>62</v>
       </c>
-      <c r="O235" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="236" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O235" s="11">
+        <v>0</v>
+      </c>
+      <c r="P235" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>251801240</v>
       </c>
@@ -12780,11 +14122,14 @@
       <c r="N236" s="9">
         <v>66</v>
       </c>
-      <c r="O236" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="237" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O236" s="11">
+        <v>0</v>
+      </c>
+      <c r="P236" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>251801241</v>
       </c>
@@ -12827,11 +14172,14 @@
       <c r="N237" s="9">
         <v>57</v>
       </c>
-      <c r="O237" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="238" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O237" s="11">
+        <v>2</v>
+      </c>
+      <c r="P237" s="12" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>251801242</v>
       </c>
@@ -12874,11 +14222,14 @@
       <c r="N238" s="9">
         <v>38</v>
       </c>
-      <c r="O238" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="239" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O238" s="11">
+        <v>0</v>
+      </c>
+      <c r="P238" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>251801243</v>
       </c>
@@ -12921,11 +14272,14 @@
       <c r="N239" s="9">
         <v>67</v>
       </c>
-      <c r="O239" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="240" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O239" s="11">
+        <v>0</v>
+      </c>
+      <c r="P239" s="12" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>251801244</v>
       </c>
@@ -12968,11 +14322,14 @@
       <c r="N240" s="9">
         <v>68</v>
       </c>
-      <c r="O240" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="241" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O240" s="11">
+        <v>0</v>
+      </c>
+      <c r="P240" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>251801245</v>
       </c>
@@ -13015,11 +14372,14 @@
       <c r="N241" s="9">
         <v>70</v>
       </c>
-      <c r="O241" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="242" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O241" s="11">
+        <v>3</v>
+      </c>
+      <c r="P241" s="12" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>251801246</v>
       </c>
@@ -13062,11 +14422,14 @@
       <c r="N242" s="9">
         <v>64</v>
       </c>
-      <c r="O242" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="243" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O242" s="11">
+        <v>0</v>
+      </c>
+      <c r="P242" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>251801247</v>
       </c>
@@ -13109,11 +14472,14 @@
       <c r="N243" s="9">
         <v>54</v>
       </c>
-      <c r="O243" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="244" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O243" s="11">
+        <v>0</v>
+      </c>
+      <c r="P243" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>251801248</v>
       </c>
@@ -13156,11 +14522,14 @@
       <c r="N244" s="9">
         <v>62</v>
       </c>
-      <c r="O244" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="245" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O244" s="11">
+        <v>1</v>
+      </c>
+      <c r="P244" s="12" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>251801249</v>
       </c>
@@ -13203,11 +14572,14 @@
       <c r="N245" s="9">
         <v>69</v>
       </c>
-      <c r="O245" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="246" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O245" s="11">
+        <v>0</v>
+      </c>
+      <c r="P245" s="12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>251801250</v>
       </c>
@@ -13250,11 +14622,14 @@
       <c r="N246" s="9">
         <v>72</v>
       </c>
-      <c r="O246" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="247" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O246" s="13">
+        <v>0</v>
+      </c>
+      <c r="P246" s="14" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>251801251</v>
       </c>
@@ -13297,11 +14672,14 @@
       <c r="N247" s="9">
         <v>49</v>
       </c>
-      <c r="O247" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="248" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O247" s="11">
+        <v>0</v>
+      </c>
+      <c r="P247" s="12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>251801252</v>
       </c>
@@ -13344,11 +14722,14 @@
       <c r="N248" s="9">
         <v>59</v>
       </c>
-      <c r="O248" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="249" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O248" s="15">
+        <v>2</v>
+      </c>
+      <c r="P248" s="16" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>251801253</v>
       </c>
@@ -13391,11 +14772,14 @@
       <c r="N249" s="9">
         <v>33</v>
       </c>
-      <c r="O249" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="250" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O249" s="13">
+        <v>3</v>
+      </c>
+      <c r="P249" s="14" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>251801254</v>
       </c>
@@ -13438,11 +14822,14 @@
       <c r="N250" s="9">
         <v>72</v>
       </c>
-      <c r="O250" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="251" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O250" s="11">
+        <v>0</v>
+      </c>
+      <c r="P250" s="12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>251801255</v>
       </c>
@@ -13485,11 +14872,14 @@
       <c r="N251" s="9">
         <v>62</v>
       </c>
-      <c r="O251" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="252" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O251" s="11">
+        <v>0</v>
+      </c>
+      <c r="P251" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>251801256</v>
       </c>
@@ -13532,11 +14922,14 @@
       <c r="N252" s="9">
         <v>61</v>
       </c>
-      <c r="O252" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="253" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O252" s="11">
+        <v>2</v>
+      </c>
+      <c r="P252" s="14" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>251801257</v>
       </c>
@@ -13579,11 +14972,14 @@
       <c r="N253" s="9">
         <v>68</v>
       </c>
-      <c r="O253" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="254" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O253" s="11">
+        <v>0</v>
+      </c>
+      <c r="P253" s="12" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>251801258</v>
       </c>
@@ -13626,11 +15022,14 @@
       <c r="N254" s="9">
         <v>52</v>
       </c>
-      <c r="O254" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="255" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O254" s="11">
+        <v>0</v>
+      </c>
+      <c r="P254" s="12" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>251801259</v>
       </c>
@@ -13673,11 +15072,14 @@
       <c r="N255" s="9">
         <v>52</v>
       </c>
-      <c r="O255" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="256" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O255" s="11">
+        <v>0</v>
+      </c>
+      <c r="P255" s="12" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>251801260</v>
       </c>
@@ -13720,11 +15122,14 @@
       <c r="N256" s="9">
         <v>46</v>
       </c>
-      <c r="O256" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="257" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O256" s="11">
+        <v>1</v>
+      </c>
+      <c r="P256" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>251801261</v>
       </c>
@@ -13767,11 +15172,14 @@
       <c r="N257" s="9">
         <v>51</v>
       </c>
-      <c r="O257" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="258" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O257" s="11">
+        <v>0</v>
+      </c>
+      <c r="P257" s="12" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>251801262</v>
       </c>
@@ -13814,11 +15222,14 @@
       <c r="N258" s="9">
         <v>64</v>
       </c>
-      <c r="O258" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="259" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O258" s="11">
+        <v>4</v>
+      </c>
+      <c r="P258" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>251801263</v>
       </c>
@@ -13861,11 +15272,14 @@
       <c r="N259" s="9">
         <v>73</v>
       </c>
-      <c r="O259" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="260" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O259" s="11">
+        <v>0</v>
+      </c>
+      <c r="P259" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>251801264</v>
       </c>
@@ -13908,11 +15322,14 @@
       <c r="N260" s="9">
         <v>54</v>
       </c>
-      <c r="O260" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="261" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O260" s="11">
+        <v>0</v>
+      </c>
+      <c r="P260" s="12" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>251801265</v>
       </c>
@@ -13955,11 +15372,14 @@
       <c r="N261" s="9">
         <v>44</v>
       </c>
-      <c r="O261" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="262" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O261" s="11">
+        <v>2</v>
+      </c>
+      <c r="P261" s="12" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>251801266</v>
       </c>
@@ -14002,11 +15422,14 @@
       <c r="N262" s="9">
         <v>59</v>
       </c>
-      <c r="O262" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="263" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O262" s="11">
+        <v>0</v>
+      </c>
+      <c r="P262" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>251801268</v>
       </c>
@@ -14049,11 +15472,14 @@
       <c r="N263" s="9">
         <v>38</v>
       </c>
-      <c r="O263" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="264" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O263" s="11">
+        <v>2</v>
+      </c>
+      <c r="P263" s="12" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>251801269</v>
       </c>
@@ -14096,11 +15522,14 @@
       <c r="N264" s="9">
         <v>55</v>
       </c>
-      <c r="O264" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="265" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O264" s="11">
+        <v>0</v>
+      </c>
+      <c r="P264" s="12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>251801270</v>
       </c>
@@ -14143,11 +15572,14 @@
       <c r="N265" s="9">
         <v>38</v>
       </c>
-      <c r="O265" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="266" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O265" s="11">
+        <v>5</v>
+      </c>
+      <c r="P265" s="12" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>251801271</v>
       </c>
@@ -14190,11 +15622,14 @@
       <c r="N266" s="9">
         <v>60</v>
       </c>
-      <c r="O266" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="267" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O266" s="11">
+        <v>0</v>
+      </c>
+      <c r="P266" s="12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>251801272</v>
       </c>
@@ -14217,7 +15652,7 @@
         <v>88.89</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I267" s="7">
         <v>95.31</v>
@@ -14237,11 +15672,14 @@
       <c r="N267" s="9">
         <v>57</v>
       </c>
-      <c r="O267" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="268" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O267" s="11">
+        <v>4</v>
+      </c>
+      <c r="P267" s="12" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>251801273</v>
       </c>
@@ -14252,7 +15690,7 @@
         <v>80</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E268" s="7">
         <v>79.03</v>
@@ -14264,13 +15702,13 @@
         <v>75</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I268" s="7">
         <v>83.33</v>
       </c>
       <c r="J268" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K268" s="7">
         <v>85.71</v>
@@ -14284,11 +15722,14 @@
       <c r="N268" s="9">
         <v>45</v>
       </c>
-      <c r="O268" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="269" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O268" s="11">
+        <v>2</v>
+      </c>
+      <c r="P268" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>251801274</v>
       </c>
@@ -14331,11 +15772,14 @@
       <c r="N269" s="9">
         <v>55</v>
       </c>
-      <c r="O269" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="270" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O269" s="11">
+        <v>0</v>
+      </c>
+      <c r="P269" s="12" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>251801275</v>
       </c>
@@ -14364,7 +15808,7 @@
         <v>70.31</v>
       </c>
       <c r="J270" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K270" s="7">
         <v>81.540000000000006</v>
@@ -14378,11 +15822,14 @@
       <c r="N270" s="9">
         <v>74</v>
       </c>
-      <c r="O270" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="271" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O270" s="11">
+        <v>0</v>
+      </c>
+      <c r="P270" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>251801276</v>
       </c>
@@ -14425,11 +15872,14 @@
       <c r="N271" s="9">
         <v>65</v>
       </c>
-      <c r="O271" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="272" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O271" s="11">
+        <v>3</v>
+      </c>
+      <c r="P271" s="12" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>251801277</v>
       </c>
@@ -14472,11 +15922,14 @@
       <c r="N272" s="9">
         <v>68</v>
       </c>
-      <c r="O272" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="273" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O272" s="11">
+        <v>0</v>
+      </c>
+      <c r="P272" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>251801278</v>
       </c>
@@ -14519,11 +15972,14 @@
       <c r="N273" s="9">
         <v>56</v>
       </c>
-      <c r="O273" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O273" s="11">
+        <v>2</v>
+      </c>
+      <c r="P273" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>251801279</v>
       </c>
@@ -14566,11 +16022,14 @@
       <c r="N274" s="9">
         <v>58</v>
       </c>
-      <c r="O274" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O274" s="11">
+        <v>0</v>
+      </c>
+      <c r="P274" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>251801280</v>
       </c>
@@ -14613,11 +16072,14 @@
       <c r="N275" s="9">
         <v>50</v>
       </c>
-      <c r="O275" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O275" s="11">
+        <v>0</v>
+      </c>
+      <c r="P275" s="12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>251801281</v>
       </c>
@@ -14660,11 +16122,14 @@
       <c r="N276" s="9">
         <v>38</v>
       </c>
-      <c r="O276" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="277" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O276" s="11">
+        <v>3</v>
+      </c>
+      <c r="P276" s="12" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>251801282</v>
       </c>
@@ -14707,11 +16172,14 @@
       <c r="N277" s="9">
         <v>70</v>
       </c>
-      <c r="O277" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="278" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O277" s="11">
+        <v>1</v>
+      </c>
+      <c r="P277" s="12" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>251801283</v>
       </c>
@@ -14754,11 +16222,14 @@
       <c r="N278" s="9">
         <v>49</v>
       </c>
-      <c r="O278" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="279" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O278" s="11">
+        <v>6</v>
+      </c>
+      <c r="P278" s="12" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>251801285</v>
       </c>
@@ -14801,11 +16272,14 @@
       <c r="N279" s="9">
         <v>56</v>
       </c>
-      <c r="O279" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O279" s="11">
+        <v>0</v>
+      </c>
+      <c r="P279" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>251801286</v>
       </c>
@@ -14848,11 +16322,14 @@
       <c r="N280" s="9">
         <v>58</v>
       </c>
-      <c r="O280" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="281" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O280" s="11">
+        <v>0</v>
+      </c>
+      <c r="P280" s="12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>251801287</v>
       </c>
@@ -14895,11 +16372,14 @@
       <c r="N281" s="9">
         <v>61</v>
       </c>
-      <c r="O281" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="282" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O281" s="11">
+        <v>2</v>
+      </c>
+      <c r="P281" s="12" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>251801288</v>
       </c>
@@ -14942,11 +16422,14 @@
       <c r="N282" s="9">
         <v>69</v>
       </c>
-      <c r="O282" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="283" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O282" s="11">
+        <v>0</v>
+      </c>
+      <c r="P282" s="12" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>251801289</v>
       </c>
@@ -14989,11 +16472,14 @@
       <c r="N283" s="9">
         <v>56</v>
       </c>
-      <c r="O283" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="284" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O283" s="11">
+        <v>4</v>
+      </c>
+      <c r="P283" s="14" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>251801290</v>
       </c>
@@ -15036,11 +16522,14 @@
       <c r="N284" s="9">
         <v>51</v>
       </c>
-      <c r="O284" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="285" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O284" s="11">
+        <v>1</v>
+      </c>
+      <c r="P284" s="12" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>251801291</v>
       </c>
@@ -15083,11 +16572,14 @@
       <c r="N285" s="9">
         <v>58</v>
       </c>
-      <c r="O285" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O285" s="11">
+        <v>0</v>
+      </c>
+      <c r="P285" s="12" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>251801292</v>
       </c>
@@ -15130,11 +16622,14 @@
       <c r="N286" s="9">
         <v>62</v>
       </c>
-      <c r="O286" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="287" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O286" s="11">
+        <v>0</v>
+      </c>
+      <c r="P286" s="12" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>251801293</v>
       </c>
@@ -15177,11 +16672,14 @@
       <c r="N287" s="9">
         <v>50</v>
       </c>
-      <c r="O287" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O287" s="11">
+        <v>4</v>
+      </c>
+      <c r="P287" s="12" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>251801294</v>
       </c>
@@ -15224,11 +16722,14 @@
       <c r="N288" s="9">
         <v>58</v>
       </c>
-      <c r="O288" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="289" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O288" s="13">
+        <v>1</v>
+      </c>
+      <c r="P288" s="14" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>251801295</v>
       </c>
@@ -15271,11 +16772,14 @@
       <c r="N289" s="9">
         <v>58</v>
       </c>
-      <c r="O289" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="290" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O289" s="11">
+        <v>0</v>
+      </c>
+      <c r="P289" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>251801296</v>
       </c>
@@ -15318,11 +16822,14 @@
       <c r="N290" s="9">
         <v>59</v>
       </c>
-      <c r="O290" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="291" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O290" s="11">
+        <v>0</v>
+      </c>
+      <c r="P290" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>251801297</v>
       </c>
@@ -15365,11 +16872,14 @@
       <c r="N291" s="9">
         <v>56</v>
       </c>
-      <c r="O291" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="292" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O291" s="15">
+        <v>2</v>
+      </c>
+      <c r="P291" s="16" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>251801298</v>
       </c>
@@ -15412,11 +16922,14 @@
       <c r="N292" s="9">
         <v>73</v>
       </c>
-      <c r="O292" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="293" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O292" s="13">
+        <v>0</v>
+      </c>
+      <c r="P292" s="14" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>251801299</v>
       </c>
@@ -15459,11 +16972,14 @@
       <c r="N293" s="9">
         <v>75</v>
       </c>
-      <c r="O293" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="294" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O293" s="18">
+        <v>0</v>
+      </c>
+      <c r="P293" s="17" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>251801300</v>
       </c>
@@ -15506,11 +17022,14 @@
       <c r="N294" s="9">
         <v>61</v>
       </c>
-      <c r="O294" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="295" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O294" s="15">
+        <v>4</v>
+      </c>
+      <c r="P294" s="16" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>251801301</v>
       </c>
@@ -15553,11 +17072,14 @@
       <c r="N295" s="9">
         <v>59</v>
       </c>
-      <c r="O295" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="296" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O295" s="11">
+        <v>0</v>
+      </c>
+      <c r="P295" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>251801302</v>
       </c>
@@ -15600,11 +17122,14 @@
       <c r="N296" s="9">
         <v>41</v>
       </c>
-      <c r="O296" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="297" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O296" s="11">
+        <v>0</v>
+      </c>
+      <c r="P296" s="12" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>251801303</v>
       </c>
@@ -15647,11 +17172,14 @@
       <c r="N297" s="9">
         <v>39</v>
       </c>
-      <c r="O297" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="298" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O297" s="11">
+        <v>3</v>
+      </c>
+      <c r="P297" s="12" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>251801304</v>
       </c>
@@ -15694,11 +17222,14 @@
       <c r="N298" s="9">
         <v>39</v>
       </c>
-      <c r="O298" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="299" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O298" s="13">
+        <v>3</v>
+      </c>
+      <c r="P298" s="14" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>251801305</v>
       </c>
@@ -15741,11 +17272,14 @@
       <c r="N299" s="9">
         <v>72</v>
       </c>
-      <c r="O299" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="300" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O299" s="11">
+        <v>0</v>
+      </c>
+      <c r="P299" s="12" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>251801306</v>
       </c>
@@ -15788,11 +17322,14 @@
       <c r="N300" s="9">
         <v>45</v>
       </c>
-      <c r="O300" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="301" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O300" s="11">
+        <v>0</v>
+      </c>
+      <c r="P300" s="12" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>251801307</v>
       </c>
@@ -15835,11 +17372,14 @@
       <c r="N301" s="9">
         <v>50</v>
       </c>
-      <c r="O301" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="302" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O301" s="11">
+        <v>4</v>
+      </c>
+      <c r="P301" s="12" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>251801308</v>
       </c>
@@ -15882,11 +17422,14 @@
       <c r="N302" s="9">
         <v>58</v>
       </c>
-      <c r="O302" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="303" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O302" s="11">
+        <v>2</v>
+      </c>
+      <c r="P302" s="12" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>251801309</v>
       </c>
@@ -15929,11 +17472,14 @@
       <c r="N303" s="9">
         <v>43</v>
       </c>
-      <c r="O303" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="304" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O303" s="13">
+        <v>0</v>
+      </c>
+      <c r="P303" s="14" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>251801310</v>
       </c>
@@ -15976,11 +17522,14 @@
       <c r="N304" s="9">
         <v>62</v>
       </c>
-      <c r="O304" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="305" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O304" s="11">
+        <v>0</v>
+      </c>
+      <c r="P304" s="12" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>251801311</v>
       </c>
@@ -16009,7 +17558,7 @@
         <v>88.57</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K305" s="7">
         <v>83.33</v>
@@ -16023,11 +17572,14 @@
       <c r="N305" s="9">
         <v>68</v>
       </c>
-      <c r="O305" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="306" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O305" s="11">
+        <v>3</v>
+      </c>
+      <c r="P305" s="12" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>251801312</v>
       </c>
@@ -16070,11 +17622,14 @@
       <c r="N306" s="9">
         <v>54</v>
       </c>
-      <c r="O306" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="307" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O306" s="11">
+        <v>0</v>
+      </c>
+      <c r="P306" s="12" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>251801313</v>
       </c>
@@ -16117,11 +17672,14 @@
       <c r="N307" s="9">
         <v>56</v>
       </c>
-      <c r="O307" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="308" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O307" s="11">
+        <v>1</v>
+      </c>
+      <c r="P307" s="12" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>251801314</v>
       </c>
@@ -16150,7 +17708,7 @@
         <v>88.57</v>
       </c>
       <c r="J308" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K308" s="7">
         <v>86.57</v>
@@ -16164,11 +17722,14 @@
       <c r="N308" s="9">
         <v>72</v>
       </c>
-      <c r="O308" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="309" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O308" s="11">
+        <v>1</v>
+      </c>
+      <c r="P308" s="12" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>251801315</v>
       </c>
@@ -16211,11 +17772,14 @@
       <c r="N309" s="9">
         <v>68</v>
       </c>
-      <c r="O309" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="310" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O309" s="11">
+        <v>0</v>
+      </c>
+      <c r="P309" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>251801316</v>
       </c>
@@ -16258,11 +17822,14 @@
       <c r="N310" s="9">
         <v>42</v>
       </c>
-      <c r="O310" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="311" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O310" s="11">
+        <v>1</v>
+      </c>
+      <c r="P310" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>251801317</v>
       </c>
@@ -16305,11 +17872,14 @@
       <c r="N311" s="9">
         <v>64</v>
       </c>
-      <c r="O311" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="312" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O311" s="13">
+        <v>6</v>
+      </c>
+      <c r="P311" s="14" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>251801318</v>
       </c>
@@ -16352,11 +17922,14 @@
       <c r="N312" s="9">
         <v>49</v>
       </c>
-      <c r="O312" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="313" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O312" s="11">
+        <v>0</v>
+      </c>
+      <c r="P312" s="12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>251801319</v>
       </c>
@@ -16399,11 +17972,14 @@
       <c r="N313" s="9">
         <v>57</v>
       </c>
-      <c r="O313" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="314" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O313" s="11">
+        <v>1</v>
+      </c>
+      <c r="P313" s="12" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="314" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>251801320</v>
       </c>
@@ -16446,11 +18022,14 @@
       <c r="N314" s="9">
         <v>44</v>
       </c>
-      <c r="O314" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="315" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O314" s="15">
+        <v>3</v>
+      </c>
+      <c r="P314" s="16" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>251801322</v>
       </c>
@@ -16493,11 +18072,14 @@
       <c r="N315" s="9">
         <v>74</v>
       </c>
-      <c r="O315" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="316" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O315" s="11">
+        <v>0</v>
+      </c>
+      <c r="P315" s="12" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>251801323</v>
       </c>
@@ -16540,11 +18122,14 @@
       <c r="N316" s="9">
         <v>38</v>
       </c>
-      <c r="O316" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="317" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O316" s="11">
+        <v>0</v>
+      </c>
+      <c r="P316" s="12" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>251801324</v>
       </c>
@@ -16587,11 +18172,14 @@
       <c r="N317" s="9">
         <v>59</v>
       </c>
-      <c r="O317" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="318" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O317" s="11">
+        <v>4</v>
+      </c>
+      <c r="P317" s="12" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="318" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>251801325</v>
       </c>
@@ -16634,11 +18222,14 @@
       <c r="N318" s="9">
         <v>48</v>
       </c>
-      <c r="O318" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="319" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O318" s="11">
+        <v>0</v>
+      </c>
+      <c r="P318" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="319" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>251801326</v>
       </c>
@@ -16681,11 +18272,14 @@
       <c r="N319" s="9">
         <v>50</v>
       </c>
-      <c r="O319" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="320" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O319" s="11">
+        <v>1</v>
+      </c>
+      <c r="P319" s="12" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="320" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>251801327</v>
       </c>
@@ -16728,11 +18322,14 @@
       <c r="N320" s="9">
         <v>60</v>
       </c>
-      <c r="O320" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="321" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O320" s="11">
+        <v>4</v>
+      </c>
+      <c r="P320" s="12" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>251801328</v>
       </c>
@@ -16775,11 +18372,14 @@
       <c r="N321" s="9">
         <v>52</v>
       </c>
-      <c r="O321" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="322" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O321" s="11">
+        <v>5</v>
+      </c>
+      <c r="P321" s="12" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>251801329</v>
       </c>
@@ -16822,11 +18422,14 @@
       <c r="N322" s="9">
         <v>68</v>
       </c>
-      <c r="O322" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="323" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O322" s="11">
+        <v>2</v>
+      </c>
+      <c r="P322" s="12" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>251801330</v>
       </c>
@@ -16869,11 +18472,14 @@
       <c r="N323" s="9">
         <v>64</v>
       </c>
-      <c r="O323" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="324" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O323" s="11">
+        <v>1</v>
+      </c>
+      <c r="P323" s="12" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>251801331</v>
       </c>
@@ -16916,11 +18522,14 @@
       <c r="N324" s="9">
         <v>38</v>
       </c>
-      <c r="O324" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="325" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O324" s="11">
+        <v>0</v>
+      </c>
+      <c r="P324" s="12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>251801332</v>
       </c>
@@ -16963,11 +18572,14 @@
       <c r="N325" s="9">
         <v>61</v>
       </c>
-      <c r="O325" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="326" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O325" s="11">
+        <v>0</v>
+      </c>
+      <c r="P325" s="12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>251801333</v>
       </c>
@@ -17010,11 +18622,14 @@
       <c r="N326" s="9">
         <v>59</v>
       </c>
-      <c r="O326" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="327" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O326" s="13">
+        <v>4</v>
+      </c>
+      <c r="P326" s="14" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>251801334</v>
       </c>
@@ -17057,11 +18672,14 @@
       <c r="N327" s="9">
         <v>43</v>
       </c>
-      <c r="O327" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="328" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O327" s="11">
+        <v>0</v>
+      </c>
+      <c r="P327" s="12" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>251801335</v>
       </c>
@@ -17104,11 +18722,14 @@
       <c r="N328" s="9">
         <v>75</v>
       </c>
-      <c r="O328" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="329" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O328" s="11">
+        <v>0</v>
+      </c>
+      <c r="P328" s="12" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="329" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>251801336</v>
       </c>
@@ -17151,11 +18772,14 @@
       <c r="N329" s="9">
         <v>65</v>
       </c>
-      <c r="O329" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="330" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O329" s="13">
+        <v>0</v>
+      </c>
+      <c r="P329" s="14" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="330" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>251801337</v>
       </c>
@@ -17198,11 +18822,14 @@
       <c r="N330" s="9">
         <v>42</v>
       </c>
-      <c r="O330" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="331" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O330" s="13">
+        <v>1</v>
+      </c>
+      <c r="P330" s="14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>251801338</v>
       </c>
@@ -17245,11 +18872,14 @@
       <c r="N331" s="9">
         <v>51</v>
       </c>
-      <c r="O331" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="332" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O331" s="13">
+        <v>3</v>
+      </c>
+      <c r="P331" s="14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>251801339</v>
       </c>
@@ -17292,11 +18922,14 @@
       <c r="N332" s="9">
         <v>53</v>
       </c>
-      <c r="O332" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="333" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O332" s="13">
+        <v>2</v>
+      </c>
+      <c r="P332" s="14" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>251801340</v>
       </c>
@@ -17339,11 +18972,14 @@
       <c r="N333" s="9">
         <v>72</v>
       </c>
-      <c r="O333" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="334" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O333" s="13">
+        <v>0</v>
+      </c>
+      <c r="P333" s="14" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>251801341</v>
       </c>
@@ -17386,11 +19022,14 @@
       <c r="N334" s="9">
         <v>60</v>
       </c>
-      <c r="O334" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="335" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O334" s="15">
+        <v>1</v>
+      </c>
+      <c r="P334" s="16" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>251801342</v>
       </c>
@@ -17433,11 +19072,14 @@
       <c r="N335" s="9">
         <v>59</v>
       </c>
-      <c r="O335" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="336" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O335" s="11">
+        <v>0</v>
+      </c>
+      <c r="P335" s="12" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>251801343</v>
       </c>
@@ -17480,11 +19122,14 @@
       <c r="N336" s="9">
         <v>45</v>
       </c>
-      <c r="O336" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="337" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O336" s="11">
+        <v>1</v>
+      </c>
+      <c r="P336" s="12" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>251801344</v>
       </c>
@@ -17527,11 +19172,14 @@
       <c r="N337" s="9">
         <v>52</v>
       </c>
-      <c r="O337" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="338" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O337" s="11">
+        <v>0</v>
+      </c>
+      <c r="P337" s="12" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>251801345</v>
       </c>
@@ -17574,11 +19222,14 @@
       <c r="N338" s="9">
         <v>71</v>
       </c>
-      <c r="O338" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="339" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O338" s="11">
+        <v>0</v>
+      </c>
+      <c r="P338" s="12" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>251801346</v>
       </c>
@@ -17621,11 +19272,14 @@
       <c r="N339" s="9">
         <v>38</v>
       </c>
-      <c r="O339" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="340" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O339" s="11">
+        <v>2</v>
+      </c>
+      <c r="P339" s="12" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>251801347</v>
       </c>
@@ -17668,11 +19322,14 @@
       <c r="N340" s="9">
         <v>68</v>
       </c>
-      <c r="O340" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="341" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O340" s="11">
+        <v>0</v>
+      </c>
+      <c r="P340" s="12" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>251801348</v>
       </c>
@@ -17695,7 +19352,7 @@
         <v>92.11</v>
       </c>
       <c r="H341" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I341" s="7">
         <v>92.86</v>
@@ -17715,11 +19372,14 @@
       <c r="N341" s="9">
         <v>56</v>
       </c>
-      <c r="O341" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="342" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O341" s="11">
+        <v>4</v>
+      </c>
+      <c r="P341" s="12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>251801349</v>
       </c>
@@ -17762,11 +19422,14 @@
       <c r="N342" s="9">
         <v>47</v>
       </c>
-      <c r="O342" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="343" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O342" s="11">
+        <v>3</v>
+      </c>
+      <c r="P342" s="12" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>251801350</v>
       </c>
@@ -17809,11 +19472,14 @@
       <c r="N343" s="9">
         <v>48</v>
       </c>
-      <c r="O343" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="344" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O343" s="11">
+        <v>1</v>
+      </c>
+      <c r="P343" s="12" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>251801351</v>
       </c>
@@ -17856,11 +19522,14 @@
       <c r="N344" s="9">
         <v>57</v>
       </c>
-      <c r="O344" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="345" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O344" s="11">
+        <v>0</v>
+      </c>
+      <c r="P344" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>251801352</v>
       </c>
@@ -17903,11 +19572,14 @@
       <c r="N345" s="9">
         <v>66</v>
       </c>
-      <c r="O345" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="346" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O345" s="13">
+        <v>1</v>
+      </c>
+      <c r="P345" s="14" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>251801353</v>
       </c>
@@ -17950,11 +19622,14 @@
       <c r="N346" s="9">
         <v>57</v>
       </c>
-      <c r="O346" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="347" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O346" s="18">
+        <v>2</v>
+      </c>
+      <c r="P346" s="17" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>251801354</v>
       </c>
@@ -17997,11 +19672,14 @@
       <c r="N347" s="9">
         <v>55</v>
       </c>
-      <c r="O347" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="348" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O347" s="15">
+        <v>0</v>
+      </c>
+      <c r="P347" s="16" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>251801355</v>
       </c>
@@ -18024,7 +19702,7 @@
         <v>71.430000000000007</v>
       </c>
       <c r="H348" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I348" s="7">
         <v>72.22</v>
@@ -18044,11 +19722,14 @@
       <c r="N348" s="9">
         <v>60</v>
       </c>
-      <c r="O348" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="349" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O348" s="11">
+        <v>0</v>
+      </c>
+      <c r="P348" s="14" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>251801356</v>
       </c>
@@ -18091,11 +19772,14 @@
       <c r="N349" s="9">
         <v>44</v>
       </c>
-      <c r="O349" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="350" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O349" s="11">
+        <v>7</v>
+      </c>
+      <c r="P349" s="12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>251801357</v>
       </c>
@@ -18138,11 +19822,14 @@
       <c r="N350" s="9">
         <v>70</v>
       </c>
-      <c r="O350" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="351" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O350" s="11">
+        <v>1</v>
+      </c>
+      <c r="P350" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="351" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>251801358</v>
       </c>
@@ -18185,11 +19872,14 @@
       <c r="N351" s="9">
         <v>55</v>
       </c>
-      <c r="O351" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="352" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O351" s="13">
+        <v>0</v>
+      </c>
+      <c r="P351" s="14" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>251801359</v>
       </c>
@@ -18232,11 +19922,14 @@
       <c r="N352" s="9">
         <v>67</v>
       </c>
-      <c r="O352" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="353" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O352" s="11">
+        <v>0</v>
+      </c>
+      <c r="P352" s="14" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="353" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>251801360</v>
       </c>
@@ -18279,11 +19972,14 @@
       <c r="N353" s="9">
         <v>73</v>
       </c>
-      <c r="O353" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="354" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O353" s="11">
+        <v>6</v>
+      </c>
+      <c r="P353" s="12" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="354" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>251801361</v>
       </c>
@@ -18326,11 +20022,14 @@
       <c r="N354" s="9">
         <v>60</v>
       </c>
-      <c r="O354" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="355" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O354" s="11">
+        <v>2</v>
+      </c>
+      <c r="P354" s="12" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>251801362</v>
       </c>
@@ -18373,11 +20072,14 @@
       <c r="N355" s="9">
         <v>47</v>
       </c>
-      <c r="O355" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="356" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O355" s="11">
+        <v>2</v>
+      </c>
+      <c r="P355" s="12" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>251801363</v>
       </c>
@@ -18420,11 +20122,14 @@
       <c r="N356" s="9">
         <v>50</v>
       </c>
-      <c r="O356" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="357" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O356" s="11">
+        <v>0</v>
+      </c>
+      <c r="P356" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>251801364</v>
       </c>
@@ -18467,11 +20172,14 @@
       <c r="N357" s="9">
         <v>65</v>
       </c>
-      <c r="O357" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="358" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O357" s="11">
+        <v>0</v>
+      </c>
+      <c r="P357" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>251801365</v>
       </c>
@@ -18506,7 +20214,7 @@
         <v>80</v>
       </c>
       <c r="L358" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M358" s="7">
         <v>77.78</v>
@@ -18514,11 +20222,14 @@
       <c r="N358" s="9">
         <v>38</v>
       </c>
-      <c r="O358" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="359" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O358" s="11">
+        <v>2</v>
+      </c>
+      <c r="P358" s="12" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="359" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>251801366</v>
       </c>
@@ -18561,11 +20272,14 @@
       <c r="N359" s="9">
         <v>33</v>
       </c>
-      <c r="O359" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="360" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O359" s="11">
+        <v>5</v>
+      </c>
+      <c r="P359" s="12" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>251801367</v>
       </c>
@@ -18608,11 +20322,14 @@
       <c r="N360" s="9">
         <v>54</v>
       </c>
-      <c r="O360" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="361" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O360" s="11">
+        <v>0</v>
+      </c>
+      <c r="P360" s="12" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="361" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>251801368</v>
       </c>
@@ -18655,11 +20372,14 @@
       <c r="N361" s="9">
         <v>38</v>
       </c>
-      <c r="O361" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="362" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O361" s="11">
+        <v>0</v>
+      </c>
+      <c r="P361" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="362" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>251801369</v>
       </c>
@@ -18702,11 +20422,14 @@
       <c r="N362" s="9">
         <v>69</v>
       </c>
-      <c r="O362" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="363" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O362" s="11">
+        <v>0</v>
+      </c>
+      <c r="P362" s="14" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="363" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>251801370</v>
       </c>
@@ -18749,11 +20472,14 @@
       <c r="N363" s="9">
         <v>58</v>
       </c>
-      <c r="O363" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="364" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O363" s="11">
+        <v>1</v>
+      </c>
+      <c r="P363" s="12" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>251801371</v>
       </c>
@@ -18796,11 +20522,14 @@
       <c r="N364" s="9">
         <v>62</v>
       </c>
-      <c r="O364" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="365" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O364" s="11">
+        <v>0</v>
+      </c>
+      <c r="P364" s="12" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="365" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>251801372</v>
       </c>
@@ -18843,11 +20572,14 @@
       <c r="N365" s="9">
         <v>45</v>
       </c>
-      <c r="O365" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="366" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O365" s="11">
+        <v>2</v>
+      </c>
+      <c r="P365" s="12" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="366" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>251801373</v>
       </c>
@@ -18890,11 +20622,14 @@
       <c r="N366" s="9">
         <v>44</v>
       </c>
-      <c r="O366" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="367" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O366" s="15">
+        <v>1</v>
+      </c>
+      <c r="P366" s="16" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="367" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>251801374</v>
       </c>
@@ -18937,11 +20672,14 @@
       <c r="N367" s="9">
         <v>38</v>
       </c>
-      <c r="O367" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="368" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O367" s="11">
+        <v>0</v>
+      </c>
+      <c r="P367" s="14" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="368" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>251801375</v>
       </c>
@@ -18984,11 +20722,14 @@
       <c r="N368" s="9">
         <v>68</v>
       </c>
-      <c r="O368" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="369" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O368" s="11">
+        <v>0</v>
+      </c>
+      <c r="P368" s="12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="369" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>251801377</v>
       </c>
@@ -19031,11 +20772,14 @@
       <c r="N369" s="9">
         <v>53</v>
       </c>
-      <c r="O369" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="370" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O369" s="11">
+        <v>3</v>
+      </c>
+      <c r="P369" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="370" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>251801378</v>
       </c>
@@ -19078,11 +20822,14 @@
       <c r="N370" s="9">
         <v>72</v>
       </c>
-      <c r="O370" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="371" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O370" s="11">
+        <v>0</v>
+      </c>
+      <c r="P370" s="12" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="371" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>251801379</v>
       </c>
@@ -19125,11 +20872,14 @@
       <c r="N371" s="9">
         <v>43</v>
       </c>
-      <c r="O371" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="372" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O371" s="11">
+        <v>0</v>
+      </c>
+      <c r="P371" s="12" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="372" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>251801380</v>
       </c>
@@ -19152,7 +20902,7 @@
         <v>83.78</v>
       </c>
       <c r="H372" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I372" s="7">
         <v>74.290000000000006</v>
@@ -19172,11 +20922,14 @@
       <c r="N372" s="9">
         <v>67</v>
       </c>
-      <c r="O372" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="373" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O372" s="11">
+        <v>1</v>
+      </c>
+      <c r="P372" s="12" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="373" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>251801381</v>
       </c>
@@ -19219,11 +20972,14 @@
       <c r="N373" s="9">
         <v>64</v>
       </c>
-      <c r="O373" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="374" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O373" s="11">
+        <v>0</v>
+      </c>
+      <c r="P373" s="12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="374" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>251801382</v>
       </c>
@@ -19266,11 +21022,14 @@
       <c r="N374" s="9">
         <v>65</v>
       </c>
-      <c r="O374" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="375" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O374" s="11">
+        <v>3</v>
+      </c>
+      <c r="P374" s="12" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="375" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>251801383</v>
       </c>
@@ -19313,11 +21072,14 @@
       <c r="N375" s="9">
         <v>40</v>
       </c>
-      <c r="O375" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="376" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O375" s="11">
+        <v>0</v>
+      </c>
+      <c r="P375" s="12" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="376" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>251801384</v>
       </c>
@@ -19360,11 +21122,14 @@
       <c r="N376" s="9">
         <v>57</v>
       </c>
-      <c r="O376" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="377" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O376" s="11">
+        <v>4</v>
+      </c>
+      <c r="P376" s="12" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="377" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>251801385</v>
       </c>
@@ -19407,11 +21172,14 @@
       <c r="N377" s="9">
         <v>41</v>
       </c>
-      <c r="O377" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="378" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O377" s="11">
+        <v>5</v>
+      </c>
+      <c r="P377" s="12" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="378" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>251801386</v>
       </c>
@@ -19454,11 +21222,14 @@
       <c r="N378" s="9">
         <v>62</v>
       </c>
-      <c r="O378" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="379" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O378" s="11">
+        <v>0</v>
+      </c>
+      <c r="P378" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="379" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>251801387</v>
       </c>
@@ -19501,11 +21272,14 @@
       <c r="N379" s="9">
         <v>0</v>
       </c>
-      <c r="O379" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="380" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O379" s="13">
+        <v>2</v>
+      </c>
+      <c r="P379" s="14" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="380" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>251801388</v>
       </c>
@@ -19548,11 +21322,14 @@
       <c r="N380" s="9">
         <v>38</v>
       </c>
-      <c r="O380" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="381" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O380" s="11">
+        <v>0</v>
+      </c>
+      <c r="P380" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="381" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>251801389</v>
       </c>
@@ -19595,11 +21372,14 @@
       <c r="N381" s="9">
         <v>50</v>
       </c>
-      <c r="O381" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="382" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O381" s="11">
+        <v>0</v>
+      </c>
+      <c r="P381" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="382" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>251801391</v>
       </c>
@@ -19642,11 +21422,14 @@
       <c r="N382" s="9">
         <v>48</v>
       </c>
-      <c r="O382" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="383" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O382" s="11">
+        <v>5</v>
+      </c>
+      <c r="P382" s="12" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="383" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>251801392</v>
       </c>
@@ -19689,11 +21472,14 @@
       <c r="N383" s="9">
         <v>48</v>
       </c>
-      <c r="O383" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="384" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O383" s="11">
+        <v>5</v>
+      </c>
+      <c r="P383" s="12" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="384" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>251801393</v>
       </c>
@@ -19716,7 +21502,7 @@
         <v>81.58</v>
       </c>
       <c r="H384" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I384" s="7">
         <v>91.67</v>
@@ -19736,11 +21522,14 @@
       <c r="N384" s="9">
         <v>71</v>
       </c>
-      <c r="O384" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="385" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O384" s="11">
+        <v>3</v>
+      </c>
+      <c r="P384" s="12" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="385" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>251801394</v>
       </c>
@@ -19783,11 +21572,14 @@
       <c r="N385" s="9">
         <v>67</v>
       </c>
-      <c r="O385" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="386" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O385" s="18">
+        <v>2</v>
+      </c>
+      <c r="P385" s="17" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="386" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>251801395</v>
       </c>
@@ -19830,11 +21622,14 @@
       <c r="N386" s="9">
         <v>62</v>
       </c>
-      <c r="O386" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="387" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O386" s="11">
+        <v>0</v>
+      </c>
+      <c r="P386" s="12" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="387" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>251801501</v>
       </c>
@@ -19877,11 +21672,14 @@
       <c r="N387" s="9">
         <v>38</v>
       </c>
-      <c r="O387" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="388" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O387" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P387" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="388" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>251801502</v>
       </c>
@@ -19924,11 +21722,14 @@
       <c r="N388" s="9">
         <v>49</v>
       </c>
-      <c r="O388" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="389" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O388" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P388" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="389" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>251801503</v>
       </c>
@@ -19971,11 +21772,14 @@
       <c r="N389" s="9">
         <v>48</v>
       </c>
-      <c r="O389" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="390" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O389" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P389" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="390" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>251801504</v>
       </c>
@@ -20018,11 +21822,14 @@
       <c r="N390" s="9">
         <v>73</v>
       </c>
-      <c r="O390" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="391" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O390" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P390" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="391" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>251801505</v>
       </c>
@@ -20065,11 +21872,14 @@
       <c r="N391" s="9">
         <v>10</v>
       </c>
-      <c r="O391" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="392" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O391" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P391" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="392" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>251801506</v>
       </c>
@@ -20092,7 +21902,7 @@
         <v>83.33</v>
       </c>
       <c r="H392" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I392" s="7">
         <v>85.94</v>
@@ -20112,11 +21922,14 @@
       <c r="N392" s="9">
         <v>50</v>
       </c>
-      <c r="O392" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="393" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O392" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P392" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="393" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>251801507</v>
       </c>
@@ -20159,11 +21972,14 @@
       <c r="N393" s="9">
         <v>51</v>
       </c>
-      <c r="O393" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="394" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O393" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P393" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="394" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>251801508</v>
       </c>
@@ -20206,11 +22022,14 @@
       <c r="N394" s="9">
         <v>57</v>
       </c>
-      <c r="O394" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="395" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O394" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P394" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="395" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>251801509</v>
       </c>
@@ -20253,11 +22072,14 @@
       <c r="N395" s="9">
         <v>54</v>
       </c>
-      <c r="O395" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="396" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O395" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P395" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>251801510</v>
       </c>
@@ -20300,11 +22122,14 @@
       <c r="N396" s="9">
         <v>44</v>
       </c>
-      <c r="O396" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="397" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O396" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P396" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>251801511</v>
       </c>
@@ -20347,11 +22172,14 @@
       <c r="N397" s="9">
         <v>51</v>
       </c>
-      <c r="O397" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="398" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O397" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P397" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>251801512</v>
       </c>
@@ -20394,11 +22222,14 @@
       <c r="N398" s="9">
         <v>38</v>
       </c>
-      <c r="O398" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="399" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O398" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P398" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>251801513</v>
       </c>
@@ -20441,11 +22272,14 @@
       <c r="N399" s="9">
         <v>40</v>
       </c>
-      <c r="O399" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="400" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O399" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P399" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>251801514</v>
       </c>
@@ -20488,11 +22322,14 @@
       <c r="N400" s="9">
         <v>52</v>
       </c>
-      <c r="O400" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="401" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O400" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P400" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>251801515</v>
       </c>
@@ -20515,13 +22352,13 @@
         <v>94.74</v>
       </c>
       <c r="H401" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I401" s="6">
         <v>92.86</v>
       </c>
       <c r="J401" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K401" s="6">
         <v>90.77</v>
@@ -20535,11 +22372,14 @@
       <c r="N401" s="9">
         <v>43</v>
       </c>
-      <c r="O401" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="402" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O401" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P401" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="402" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>251801701</v>
       </c>
@@ -20582,11 +22422,14 @@
       <c r="N402" s="6">
         <v>50</v>
       </c>
-      <c r="O402" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="403" spans="1:15" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O402" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P402" s="11" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="403" spans="1:16" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>251801901</v>
       </c>
@@ -20609,13 +22452,13 @@
         <v>77.78</v>
       </c>
       <c r="H403" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I403" s="5">
         <v>79.69</v>
       </c>
       <c r="J403" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K403" s="5">
         <v>81.540000000000006</v>
@@ -20629,8 +22472,11 @@
       <c r="N403" s="6">
         <v>43</v>
       </c>
-      <c r="O403" s="5" t="s">
-        <v>415</v>
+      <c r="O403" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="P403" s="11" t="s">
+        <v>612</v>
       </c>
     </row>
   </sheetData>
